--- a/Write off stock QC.xlsx
+++ b/Write off stock QC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9AAF3FC-B1DC-4BD8-85C7-20FB1D84FBD1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8396F997-399C-4865-881A-271D6B506BF5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{09A0D57F-1F4F-4A67-AD02-CF0FEEFE867F}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="521">
   <si>
     <t>Name</t>
   </si>
@@ -1411,9 +1411,6 @@
     <t>On hold</t>
   </si>
   <si>
-    <t>Stock count adjustment 30 June 26</t>
-  </si>
-  <si>
     <t>30/07/2026_Tư FGQC_Write-off</t>
   </si>
   <si>
@@ -1580,6 +1577,12 @@
   </si>
   <si>
     <t>Credit note released waiting WH for VR return</t>
+  </si>
+  <si>
+    <t>23/5/2025_Vuqcpoly_Size thép đặt sai kích thước</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	01/06/2026_SANG QC_TBI Thiếu keo_CHờ hủy</t>
   </si>
 </sst>
 </file>
@@ -2210,7 +2213,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2221,6 +2224,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2270,6 +2274,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="18" fillId="33" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2755,6 +2768,14 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AA967156-E67F-411F-9430-CE31B28DDA10}" name="Table13" displayName="Table13" ref="A1:R218" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21" headerRowBorderDxfId="19" tableBorderDxfId="20" totalsRowBorderDxfId="18" headerRowCellStyle="Comma">
+  <autoFilter ref="A1:R218" xr:uid="{D100E3CB-680C-4696-9614-C02863D70058}">
+    <filterColumn colId="16">
+      <filters>
+        <filter val="#VALUE!"/>
+        <filter val="#N/A"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState ref="A2:R215">
     <sortCondition descending="1" ref="L1:L218"/>
   </sortState>
@@ -3106,6 +3127,9 @@
   <dimension ref="A1:R218"/>
   <sheetFormatPr defaultRowHeight="10.199999999999999"/>
   <cols>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.5703125" customWidth="1"/>
     <col min="13" max="13" width="40.42578125" customWidth="1"/>
     <col min="14" max="14" width="21.5703125" customWidth="1"/>
@@ -3116,63 +3140,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="15" t="s">
         <v>446</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="16" t="s">
         <v>458</v>
       </c>
-      <c r="O1" s="15" t="s">
-        <v>509</v>
-      </c>
-      <c r="P1" s="16" t="s">
+      <c r="O1" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="P1" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="Q1" s="17" t="s">
         <v>507</v>
       </c>
-      <c r="Q1" s="16" t="s">
-        <v>508</v>
-      </c>
-      <c r="R1" s="19" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="6" t="s">
+      <c r="R1" s="20" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" hidden="1">
+      <c r="A2" s="7" t="s">
         <v>241</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -3208,29 +3232,29 @@
       <c r="L2" s="2">
         <v>103077212</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="O2" s="21" t="s">
         <v>511</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="O2" s="20" t="s">
-        <v>512</v>
       </c>
       <c r="P2" s="3" t="str">
         <f t="shared" ref="P2:P65" si="0">LEFT(M2,FIND("_",M2)-1)</f>
         <v>18/03/2024</v>
       </c>
-      <c r="Q2" s="17">
+      <c r="Q2" s="18">
         <v>45369</v>
       </c>
-      <c r="R2" s="18">
+      <c r="R2" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-880</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:18" hidden="1">
+      <c r="A3" s="7" t="s">
         <v>244</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -3266,29 +3290,29 @@
       <c r="L3" s="2">
         <v>21469293</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="O3" s="7" t="s">
-        <v>512</v>
+      <c r="O3" s="8" t="s">
+        <v>511</v>
       </c>
       <c r="P3" s="1" t="str">
         <f t="shared" si="0"/>
         <v>18/03/2024</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="18">
         <v>45369</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-880</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:18" hidden="1">
+      <c r="A4" s="7" t="s">
         <v>247</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -3324,29 +3348,29 @@
       <c r="L4" s="2">
         <v>83936292</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="O4" s="7" t="s">
-        <v>512</v>
+      <c r="O4" s="8" t="s">
+        <v>511</v>
       </c>
       <c r="P4" s="1" t="str">
         <f t="shared" si="0"/>
         <v>18/03/2024</v>
       </c>
-      <c r="Q4" s="17">
+      <c r="Q4" s="18">
         <v>45369</v>
       </c>
-      <c r="R4" s="18">
+      <c r="R4" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-880</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:18" hidden="1">
+      <c r="A5" s="7" t="s">
         <v>434</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -3383,28 +3407,28 @@
         <v>110277485</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="N5" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="N5" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O5" s="7" t="s">
-        <v>514</v>
+      <c r="O5" s="8" t="s">
+        <v>513</v>
       </c>
       <c r="P5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>23/09/2025</v>
       </c>
-      <c r="Q5" s="17">
+      <c r="Q5" s="18">
         <v>45923</v>
       </c>
-      <c r="R5" s="18">
+      <c r="R5" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-326</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:18" hidden="1">
+      <c r="A6" s="7" t="s">
         <v>437</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -3441,28 +3465,28 @@
         <v>104070654</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="N6" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="N6" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O6" s="7" t="s">
-        <v>514</v>
+      <c r="O6" s="8" t="s">
+        <v>513</v>
       </c>
       <c r="P6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>23/09/2025</v>
       </c>
-      <c r="Q6" s="17">
+      <c r="Q6" s="18">
         <v>45923</v>
       </c>
-      <c r="R6" s="18">
+      <c r="R6" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-326</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:18" hidden="1">
+      <c r="A7" s="7" t="s">
         <v>222</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -3499,28 +3523,28 @@
         <v>48782180</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="N7" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O7" s="7" t="s">
-        <v>515</v>
+      <c r="O7" s="8" t="s">
+        <v>514</v>
       </c>
       <c r="P7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>30/07/2026</v>
       </c>
-      <c r="Q7" s="17">
+      <c r="Q7" s="18">
         <v>46233</v>
       </c>
-      <c r="R7" s="18">
+      <c r="R7" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-16</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:18" hidden="1">
+      <c r="A8" s="6" t="s">
         <v>210</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -3556,29 +3580,29 @@
       <c r="L8" s="2">
         <v>35210000</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O8" s="7" t="s">
-        <v>516</v>
+      <c r="O8" s="8" t="s">
+        <v>515</v>
       </c>
       <c r="P8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>06/05/2025</v>
       </c>
-      <c r="Q8" s="17">
+      <c r="Q8" s="18">
         <v>45783</v>
       </c>
-      <c r="R8" s="18">
+      <c r="R8" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-466</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:18" hidden="1">
+      <c r="A9" s="7" t="s">
         <v>213</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -3615,26 +3639,26 @@
         <v>20699100</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="N9" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="N9" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O9" s="7"/>
+      <c r="O9" s="8"/>
       <c r="P9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>06/08/2026</v>
       </c>
-      <c r="Q9" s="17">
+      <c r="Q9" s="18">
         <v>46240</v>
       </c>
-      <c r="R9" s="18">
+      <c r="R9" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-9</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:18" hidden="1">
+      <c r="A10" s="7" t="s">
         <v>76</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -3671,28 +3695,28 @@
         <v>17904479</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="N10" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="N10" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O10" s="7" t="s">
-        <v>513</v>
+      <c r="O10" s="8" t="s">
+        <v>512</v>
       </c>
       <c r="P10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>8/7/2025</v>
       </c>
-      <c r="Q10" s="17">
+      <c r="Q10" s="18">
         <v>45846</v>
       </c>
-      <c r="R10" s="18">
+      <c r="R10" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-403</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:18" hidden="1">
+      <c r="A11" s="7" t="s">
         <v>408</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -3729,26 +3753,26 @@
         <v>17851786</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="N11" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="N11" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O11" s="7"/>
+      <c r="O11" s="8"/>
       <c r="P11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>27/06/2026</v>
       </c>
-      <c r="Q11" s="17">
+      <c r="Q11" s="18">
         <v>46200</v>
       </c>
-      <c r="R11" s="18">
+      <c r="R11" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-49</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:18" hidden="1">
+      <c r="A12" s="7" t="s">
         <v>265</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -3785,28 +3809,28 @@
         <v>16857708</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="N12" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="N12" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O12" s="7" t="s">
-        <v>513</v>
+      <c r="O12" s="8" t="s">
+        <v>512</v>
       </c>
       <c r="P12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>20/12/2025</v>
       </c>
-      <c r="Q12" s="17">
+      <c r="Q12" s="18">
         <v>46011</v>
       </c>
-      <c r="R12" s="18">
+      <c r="R12" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-238</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:18" hidden="1">
+      <c r="A13" s="7" t="s">
         <v>401</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -3843,26 +3867,26 @@
         <v>16446980</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="N13" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="N13" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O13" s="7"/>
+      <c r="O13" s="8"/>
       <c r="P13" s="1" t="str">
         <f t="shared" si="0"/>
         <v>17/3/2026</v>
       </c>
-      <c r="Q13" s="17">
+      <c r="Q13" s="18">
         <v>46098</v>
       </c>
-      <c r="R13" s="18">
+      <c r="R13" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-151</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:18" hidden="1">
+      <c r="A14" s="7" t="s">
         <v>267</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -3899,26 +3923,26 @@
         <v>11181750</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="N14" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="N14" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O14" s="7"/>
+      <c r="O14" s="8"/>
       <c r="P14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>11/10/2025</v>
       </c>
-      <c r="Q14" s="17">
+      <c r="Q14" s="18">
         <v>45941</v>
       </c>
-      <c r="R14" s="18">
+      <c r="R14" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-308</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:18" hidden="1">
+      <c r="A15" s="6" t="s">
         <v>167</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -3954,27 +3978,27 @@
       <c r="L15" s="2">
         <v>11063295</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="N15" s="7" t="s">
+      <c r="N15" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O15" s="7"/>
+      <c r="O15" s="8"/>
       <c r="P15" s="1" t="str">
         <f t="shared" si="0"/>
         <v>27/08/2025</v>
       </c>
-      <c r="Q15" s="17">
+      <c r="Q15" s="18">
         <v>45896</v>
       </c>
-      <c r="R15" s="18">
+      <c r="R15" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-353</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:18" hidden="1">
+      <c r="A16" s="7" t="s">
         <v>31</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -4010,29 +4034,29 @@
       <c r="L16" s="2">
         <v>26560286</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="M16" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="N16" s="7" t="s">
+      <c r="N16" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="O16" s="8" t="s">
         <v>518</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>519</v>
       </c>
       <c r="P16" s="1" t="str">
         <f t="shared" si="0"/>
         <v>06/03/2026</v>
       </c>
-      <c r="Q16" s="17">
+      <c r="Q16" s="18">
         <v>46087</v>
       </c>
-      <c r="R16" s="18">
+      <c r="R16" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-162</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:18" hidden="1">
+      <c r="A17" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -4068,29 +4092,29 @@
       <c r="L17" s="2">
         <v>4199519</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="M17" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="N17" s="7" t="s">
+      <c r="N17" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="O17" s="8" t="s">
         <v>518</v>
-      </c>
-      <c r="O17" s="7" t="s">
-        <v>519</v>
       </c>
       <c r="P17" s="1" t="str">
         <f t="shared" si="0"/>
         <v>06/03/2026</v>
       </c>
-      <c r="Q17" s="17">
+      <c r="Q17" s="18">
         <v>46087</v>
       </c>
-      <c r="R17" s="18">
+      <c r="R17" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-162</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:18" hidden="1">
+      <c r="A18" s="7" t="s">
         <v>207</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -4126,27 +4150,27 @@
       <c r="L18" s="2">
         <v>9747823</v>
       </c>
-      <c r="M18" s="4" t="s">
+      <c r="M18" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="N18" s="7" t="s">
+      <c r="N18" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O18" s="7"/>
+      <c r="O18" s="8"/>
       <c r="P18" s="1" t="str">
         <f t="shared" si="0"/>
         <v>10/7/2024</v>
       </c>
-      <c r="Q18" s="17">
+      <c r="Q18" s="18">
         <v>45483</v>
       </c>
-      <c r="R18" s="18">
+      <c r="R18" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-766</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:18" hidden="1">
+      <c r="A19" s="7" t="s">
         <v>128</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -4183,26 +4207,26 @@
         <v>9525917</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="N19" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="N19" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O19" s="7"/>
+      <c r="O19" s="8"/>
       <c r="P19" s="1" t="str">
         <f t="shared" si="0"/>
         <v>11/08/2026</v>
       </c>
-      <c r="Q19" s="17">
+      <c r="Q19" s="18">
         <v>46245</v>
       </c>
-      <c r="R19" s="18">
+      <c r="R19" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-4</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:18" hidden="1">
+      <c r="A20" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -4238,29 +4262,29 @@
       <c r="L20" s="2">
         <v>3536190</v>
       </c>
-      <c r="M20" s="4" t="s">
+      <c r="M20" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="N20" s="7" t="s">
+      <c r="N20" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="O20" s="8" t="s">
         <v>518</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>519</v>
       </c>
       <c r="P20" s="1" t="str">
         <f t="shared" si="0"/>
         <v>30/3/2026</v>
       </c>
-      <c r="Q20" s="17">
+      <c r="Q20" s="18">
         <v>46111</v>
       </c>
-      <c r="R20" s="18">
+      <c r="R20" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-138</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:18" hidden="1">
+      <c r="A21" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -4296,29 +4320,29 @@
       <c r="L21" s="2">
         <v>195076</v>
       </c>
-      <c r="M21" s="4" t="s">
+      <c r="M21" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="N21" s="7" t="s">
+      <c r="N21" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="O21" s="8" t="s">
         <v>518</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>519</v>
       </c>
       <c r="P21" s="1" t="str">
         <f t="shared" si="0"/>
         <v>30/3/2026</v>
       </c>
-      <c r="Q21" s="17">
+      <c r="Q21" s="18">
         <v>46111</v>
       </c>
-      <c r="R21" s="18">
+      <c r="R21" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-138</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:18" hidden="1">
+      <c r="A22" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -4354,29 +4378,29 @@
       <c r="L22" s="2">
         <v>181700</v>
       </c>
-      <c r="M22" s="4" t="s">
+      <c r="M22" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="N22" s="7" t="s">
+      <c r="N22" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="O22" s="8" t="s">
         <v>518</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>519</v>
       </c>
       <c r="P22" s="1" t="str">
         <f t="shared" si="0"/>
         <v>30/3/2026</v>
       </c>
-      <c r="Q22" s="17">
+      <c r="Q22" s="18">
         <v>46111</v>
       </c>
-      <c r="R22" s="18">
+      <c r="R22" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-138</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:18" hidden="1">
+      <c r="A23" s="7" t="s">
         <v>255</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -4413,28 +4437,28 @@
         <v>17125887</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="N23" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="N23" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="O23" s="7" t="s">
-        <v>510</v>
+      <c r="O23" s="8" t="s">
+        <v>509</v>
       </c>
       <c r="P23" s="1" t="str">
         <f t="shared" si="0"/>
         <v>11/05/2026</v>
       </c>
-      <c r="Q23" s="17">
+      <c r="Q23" s="18">
         <v>46153</v>
       </c>
-      <c r="R23" s="18">
+      <c r="R23" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-96</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:18" hidden="1">
+      <c r="A24" s="7" t="s">
         <v>80</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -4471,28 +4495,28 @@
         <v>7150708</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="N24" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="N24" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O24" s="7" t="s">
-        <v>513</v>
+      <c r="O24" s="8" t="s">
+        <v>512</v>
       </c>
       <c r="P24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>2/7/2025</v>
       </c>
-      <c r="Q24" s="17">
+      <c r="Q24" s="18">
         <v>45840</v>
       </c>
-      <c r="R24" s="18">
+      <c r="R24" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-409</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:18" hidden="1">
+      <c r="A25" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -4528,29 +4552,29 @@
       <c r="L25" s="2">
         <v>52031</v>
       </c>
-      <c r="M25" s="4" t="s">
+      <c r="M25" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N25" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O25" s="7" t="s">
+      <c r="N25" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O25" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P25" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q25" s="17">
+      <c r="Q25" s="18">
         <v>46155</v>
       </c>
-      <c r="R25" s="18">
+      <c r="R25" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="6" t="s">
+    <row r="26" spans="1:18" hidden="1">
+      <c r="A26" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -4586,29 +4610,29 @@
       <c r="L26" s="2">
         <v>104462</v>
       </c>
-      <c r="M26" s="4" t="s">
+      <c r="M26" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N26" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O26" s="7" t="s">
+      <c r="N26" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O26" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P26" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q26" s="17">
+      <c r="Q26" s="18">
         <v>46155</v>
       </c>
-      <c r="R26" s="18">
+      <c r="R26" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
-      <c r="A27" s="6" t="s">
+    <row r="27" spans="1:18" hidden="1">
+      <c r="A27" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -4644,29 +4668,29 @@
       <c r="L27" s="2">
         <v>65330</v>
       </c>
-      <c r="M27" s="4" t="s">
+      <c r="M27" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N27" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O27" s="7" t="s">
+      <c r="N27" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O27" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P27" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q27" s="17">
+      <c r="Q27" s="18">
         <v>46155</v>
       </c>
-      <c r="R27" s="18">
+      <c r="R27" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
-      <c r="A28" s="6" t="s">
+    <row r="28" spans="1:18" hidden="1">
+      <c r="A28" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -4702,29 +4726,29 @@
       <c r="L28" s="2">
         <v>230551</v>
       </c>
-      <c r="M28" s="4" t="s">
+      <c r="M28" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N28" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O28" s="7" t="s">
+      <c r="N28" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O28" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P28" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q28" s="17">
+      <c r="Q28" s="18">
         <v>46155</v>
       </c>
-      <c r="R28" s="18">
+      <c r="R28" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:18" hidden="1">
+      <c r="A29" s="7" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -4760,29 +4784,29 @@
       <c r="L29" s="2">
         <v>180383</v>
       </c>
-      <c r="M29" s="4" t="s">
+      <c r="M29" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N29" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O29" s="7" t="s">
+      <c r="N29" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O29" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P29" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q29" s="17">
+      <c r="Q29" s="18">
         <v>46155</v>
       </c>
-      <c r="R29" s="18">
+      <c r="R29" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
-      <c r="A30" s="6" t="s">
+    <row r="30" spans="1:18" hidden="1">
+      <c r="A30" s="7" t="s">
         <v>45</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -4818,29 +4842,29 @@
       <c r="L30" s="2">
         <v>48729</v>
       </c>
-      <c r="M30" s="4" t="s">
+      <c r="M30" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N30" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O30" s="7" t="s">
+      <c r="N30" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O30" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P30" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q30" s="17">
+      <c r="Q30" s="18">
         <v>46155</v>
       </c>
-      <c r="R30" s="18">
+      <c r="R30" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:18" hidden="1">
+      <c r="A31" s="7" t="s">
         <v>47</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -4876,29 +4900,29 @@
       <c r="L31" s="2">
         <v>149832</v>
       </c>
-      <c r="M31" s="4" t="s">
+      <c r="M31" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N31" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O31" s="7" t="s">
+      <c r="N31" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O31" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P31" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q31" s="17">
+      <c r="Q31" s="18">
         <v>46155</v>
       </c>
-      <c r="R31" s="18">
+      <c r="R31" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:18" hidden="1">
+      <c r="A32" s="7" t="s">
         <v>49</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -4934,29 +4958,29 @@
       <c r="L32" s="2">
         <v>143168</v>
       </c>
-      <c r="M32" s="4" t="s">
+      <c r="M32" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N32" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O32" s="7" t="s">
+      <c r="N32" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O32" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q32" s="17">
+      <c r="Q32" s="18">
         <v>46155</v>
       </c>
-      <c r="R32" s="18">
+      <c r="R32" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="33" spans="1:18">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:18" hidden="1">
+      <c r="A33" s="7" t="s">
         <v>50</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -4992,29 +5016,29 @@
       <c r="L33" s="2">
         <v>162244</v>
       </c>
-      <c r="M33" s="4" t="s">
+      <c r="M33" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N33" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O33" s="7" t="s">
+      <c r="N33" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O33" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P33" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q33" s="17">
+      <c r="Q33" s="18">
         <v>46155</v>
       </c>
-      <c r="R33" s="18">
+      <c r="R33" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="34" spans="1:18">
-      <c r="A34" s="6" t="s">
+    <row r="34" spans="1:18" hidden="1">
+      <c r="A34" s="7" t="s">
         <v>52</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -5050,29 +5074,29 @@
       <c r="L34" s="2">
         <v>128022</v>
       </c>
-      <c r="M34" s="4" t="s">
+      <c r="M34" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N34" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O34" s="7" t="s">
+      <c r="N34" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O34" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P34" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q34" s="17">
+      <c r="Q34" s="18">
         <v>46155</v>
       </c>
-      <c r="R34" s="18">
+      <c r="R34" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="35" spans="1:18">
-      <c r="A35" s="6" t="s">
+    <row r="35" spans="1:18" hidden="1">
+      <c r="A35" s="7" t="s">
         <v>58</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -5108,29 +5132,29 @@
       <c r="L35" s="2">
         <v>102459</v>
       </c>
-      <c r="M35" s="4" t="s">
+      <c r="M35" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N35" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O35" s="7" t="s">
+      <c r="N35" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O35" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q35" s="17">
+      <c r="Q35" s="18">
         <v>46155</v>
       </c>
-      <c r="R35" s="18">
+      <c r="R35" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="36" spans="1:18">
-      <c r="A36" s="6" t="s">
+    <row r="36" spans="1:18" hidden="1">
+      <c r="A36" s="7" t="s">
         <v>60</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -5166,29 +5190,29 @@
       <c r="L36" s="2">
         <v>381912</v>
       </c>
-      <c r="M36" s="4" t="s">
+      <c r="M36" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N36" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O36" s="7" t="s">
+      <c r="N36" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O36" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P36" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q36" s="17">
+      <c r="Q36" s="18">
         <v>46155</v>
       </c>
-      <c r="R36" s="18">
+      <c r="R36" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="37" spans="1:18">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:18" hidden="1">
+      <c r="A37" s="7" t="s">
         <v>63</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -5224,29 +5248,29 @@
       <c r="L37" s="2">
         <v>62653</v>
       </c>
-      <c r="M37" s="4" t="s">
+      <c r="M37" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N37" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O37" s="7" t="s">
+      <c r="N37" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O37" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P37" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q37" s="17">
+      <c r="Q37" s="18">
         <v>46155</v>
       </c>
-      <c r="R37" s="18">
+      <c r="R37" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="38" spans="1:18">
-      <c r="A38" s="6" t="s">
+    <row r="38" spans="1:18" hidden="1">
+      <c r="A38" s="7" t="s">
         <v>65</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -5282,29 +5306,29 @@
       <c r="L38" s="2">
         <v>122000</v>
       </c>
-      <c r="M38" s="4" t="s">
+      <c r="M38" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N38" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O38" s="7" t="s">
+      <c r="N38" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O38" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P38" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q38" s="17">
+      <c r="Q38" s="18">
         <v>46155</v>
       </c>
-      <c r="R38" s="18">
+      <c r="R38" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="39" spans="1:18">
-      <c r="A39" s="6" t="s">
+    <row r="39" spans="1:18" hidden="1">
+      <c r="A39" s="7" t="s">
         <v>68</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -5340,29 +5364,29 @@
       <c r="L39" s="2">
         <v>80011</v>
       </c>
-      <c r="M39" s="4" t="s">
+      <c r="M39" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N39" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O39" s="7" t="s">
+      <c r="N39" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O39" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P39" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q39" s="17">
+      <c r="Q39" s="18">
         <v>46155</v>
       </c>
-      <c r="R39" s="18">
+      <c r="R39" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="40" spans="1:18">
-      <c r="A40" s="6" t="s">
+    <row r="40" spans="1:18" hidden="1">
+      <c r="A40" s="7" t="s">
         <v>71</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -5398,29 +5422,29 @@
       <c r="L40" s="2">
         <v>87979</v>
       </c>
-      <c r="M40" s="4" t="s">
+      <c r="M40" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N40" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O40" s="7" t="s">
+      <c r="N40" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O40" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P40" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q40" s="17">
+      <c r="Q40" s="18">
         <v>46155</v>
       </c>
-      <c r="R40" s="18">
+      <c r="R40" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="41" spans="1:18">
-      <c r="A41" s="6" t="s">
+    <row r="41" spans="1:18" hidden="1">
+      <c r="A41" s="7" t="s">
         <v>73</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -5456,29 +5480,29 @@
       <c r="L41" s="2">
         <v>91100</v>
       </c>
-      <c r="M41" s="4" t="s">
+      <c r="M41" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N41" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O41" s="7" t="s">
+      <c r="N41" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O41" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P41" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q41" s="17">
+      <c r="Q41" s="18">
         <v>46155</v>
       </c>
-      <c r="R41" s="18">
+      <c r="R41" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="42" spans="1:18">
-      <c r="A42" s="6" t="s">
+    <row r="42" spans="1:18" hidden="1">
+      <c r="A42" s="7" t="s">
         <v>86</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -5514,29 +5538,29 @@
       <c r="L42" s="2">
         <v>1600000</v>
       </c>
-      <c r="M42" s="4" t="s">
+      <c r="M42" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N42" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O42" s="7" t="s">
+      <c r="N42" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O42" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P42" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q42" s="17">
+      <c r="Q42" s="18">
         <v>46155</v>
       </c>
-      <c r="R42" s="18">
+      <c r="R42" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="43" spans="1:18">
-      <c r="A43" s="6" t="s">
+    <row r="43" spans="1:18" hidden="1">
+      <c r="A43" s="7" t="s">
         <v>97</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -5572,29 +5596,29 @@
       <c r="L43" s="2">
         <v>140426</v>
       </c>
-      <c r="M43" s="4" t="s">
+      <c r="M43" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N43" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O43" s="7" t="s">
+      <c r="N43" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O43" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P43" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q43" s="17">
+      <c r="Q43" s="18">
         <v>46155</v>
       </c>
-      <c r="R43" s="18">
+      <c r="R43" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="44" spans="1:18">
-      <c r="A44" s="6" t="s">
+    <row r="44" spans="1:18" hidden="1">
+      <c r="A44" s="7" t="s">
         <v>99</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -5630,29 +5654,29 @@
       <c r="L44" s="2">
         <v>110848</v>
       </c>
-      <c r="M44" s="4" t="s">
+      <c r="M44" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N44" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O44" s="7" t="s">
+      <c r="N44" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O44" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P44" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q44" s="17">
+      <c r="Q44" s="18">
         <v>46155</v>
       </c>
-      <c r="R44" s="18">
+      <c r="R44" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="45" spans="1:18">
-      <c r="A45" s="6" t="s">
+    <row r="45" spans="1:18" hidden="1">
+      <c r="A45" s="7" t="s">
         <v>102</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -5688,29 +5712,29 @@
       <c r="L45" s="2">
         <v>106946</v>
       </c>
-      <c r="M45" s="4" t="s">
+      <c r="M45" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N45" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O45" s="7" t="s">
+      <c r="N45" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O45" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P45" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q45" s="17">
+      <c r="Q45" s="18">
         <v>46155</v>
       </c>
-      <c r="R45" s="18">
+      <c r="R45" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="46" spans="1:18">
-      <c r="A46" s="6" t="s">
+    <row r="46" spans="1:18" hidden="1">
+      <c r="A46" s="7" t="s">
         <v>104</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -5746,29 +5770,29 @@
       <c r="L46" s="2">
         <v>158283</v>
       </c>
-      <c r="M46" s="4" t="s">
+      <c r="M46" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N46" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O46" s="7" t="s">
+      <c r="N46" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O46" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P46" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q46" s="17">
+      <c r="Q46" s="18">
         <v>46155</v>
       </c>
-      <c r="R46" s="18">
+      <c r="R46" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="47" spans="1:18">
-      <c r="A47" s="6" t="s">
+    <row r="47" spans="1:18" hidden="1">
+      <c r="A47" s="7" t="s">
         <v>105</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -5804,29 +5828,29 @@
       <c r="L47" s="2">
         <v>55643</v>
       </c>
-      <c r="M47" s="4" t="s">
+      <c r="M47" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N47" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O47" s="7" t="s">
+      <c r="N47" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O47" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P47" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q47" s="17">
+      <c r="Q47" s="18">
         <v>46155</v>
       </c>
-      <c r="R47" s="18">
+      <c r="R47" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="48" spans="1:18">
-      <c r="A48" s="6" t="s">
+    <row r="48" spans="1:18" hidden="1">
+      <c r="A48" s="7" t="s">
         <v>106</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -5862,29 +5886,29 @@
       <c r="L48" s="2">
         <v>98612</v>
       </c>
-      <c r="M48" s="4" t="s">
+      <c r="M48" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N48" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O48" s="7" t="s">
+      <c r="N48" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O48" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P48" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q48" s="17">
+      <c r="Q48" s="18">
         <v>46155</v>
       </c>
-      <c r="R48" s="18">
+      <c r="R48" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="49" spans="1:18">
-      <c r="A49" s="6" t="s">
+    <row r="49" spans="1:18" hidden="1">
+      <c r="A49" s="7" t="s">
         <v>107</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -5920,29 +5944,29 @@
       <c r="L49" s="2">
         <v>635567</v>
       </c>
-      <c r="M49" s="4" t="s">
+      <c r="M49" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N49" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O49" s="7" t="s">
+      <c r="N49" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O49" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P49" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q49" s="17">
+      <c r="Q49" s="18">
         <v>46155</v>
       </c>
-      <c r="R49" s="18">
+      <c r="R49" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="50" spans="1:18">
-      <c r="A50" s="6" t="s">
+    <row r="50" spans="1:18" hidden="1">
+      <c r="A50" s="7" t="s">
         <v>109</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -5978,29 +6002,29 @@
       <c r="L50" s="2">
         <v>53409</v>
       </c>
-      <c r="M50" s="4" t="s">
+      <c r="M50" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N50" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O50" s="7" t="s">
+      <c r="N50" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O50" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P50" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q50" s="17">
+      <c r="Q50" s="18">
         <v>46155</v>
       </c>
-      <c r="R50" s="18">
+      <c r="R50" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="51" spans="1:18">
-      <c r="A51" s="6" t="s">
+    <row r="51" spans="1:18" hidden="1">
+      <c r="A51" s="7" t="s">
         <v>114</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -6036,29 +6060,29 @@
       <c r="L51" s="2">
         <v>136871</v>
       </c>
-      <c r="M51" s="4" t="s">
+      <c r="M51" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N51" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O51" s="7" t="s">
+      <c r="N51" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O51" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P51" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q51" s="17">
+      <c r="Q51" s="18">
         <v>46155</v>
       </c>
-      <c r="R51" s="18">
+      <c r="R51" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="52" spans="1:18">
-      <c r="A52" s="6" t="s">
+    <row r="52" spans="1:18" hidden="1">
+      <c r="A52" s="7" t="s">
         <v>117</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -6094,29 +6118,29 @@
       <c r="L52" s="2">
         <v>233203</v>
       </c>
-      <c r="M52" s="4" t="s">
+      <c r="M52" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N52" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O52" s="7" t="s">
+      <c r="N52" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O52" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P52" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q52" s="17">
+      <c r="Q52" s="18">
         <v>46155</v>
       </c>
-      <c r="R52" s="18">
+      <c r="R52" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="53" spans="1:18">
-      <c r="A53" s="6" t="s">
+    <row r="53" spans="1:18" hidden="1">
+      <c r="A53" s="7" t="s">
         <v>119</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -6152,29 +6176,29 @@
       <c r="L53" s="2">
         <v>115948</v>
       </c>
-      <c r="M53" s="4" t="s">
+      <c r="M53" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N53" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O53" s="7" t="s">
+      <c r="N53" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O53" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P53" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q53" s="17">
+      <c r="Q53" s="18">
         <v>46155</v>
       </c>
-      <c r="R53" s="18">
+      <c r="R53" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="54" spans="1:18">
-      <c r="A54" s="6" t="s">
+    <row r="54" spans="1:18" hidden="1">
+      <c r="A54" s="7" t="s">
         <v>121</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -6210,29 +6234,29 @@
       <c r="L54" s="2">
         <v>120239</v>
       </c>
-      <c r="M54" s="4" t="s">
+      <c r="M54" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N54" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O54" s="7" t="s">
+      <c r="N54" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O54" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P54" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q54" s="17">
+      <c r="Q54" s="18">
         <v>46155</v>
       </c>
-      <c r="R54" s="18">
+      <c r="R54" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="55" spans="1:18">
-      <c r="A55" s="6" t="s">
+    <row r="55" spans="1:18" hidden="1">
+      <c r="A55" s="7" t="s">
         <v>123</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -6268,29 +6292,29 @@
       <c r="L55" s="2">
         <v>117971</v>
       </c>
-      <c r="M55" s="4" t="s">
+      <c r="M55" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N55" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O55" s="7" t="s">
+      <c r="N55" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O55" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P55" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q55" s="17">
+      <c r="Q55" s="18">
         <v>46155</v>
       </c>
-      <c r="R55" s="18">
+      <c r="R55" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="56" spans="1:18">
-      <c r="A56" s="6" t="s">
+    <row r="56" spans="1:18" hidden="1">
+      <c r="A56" s="7" t="s">
         <v>130</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -6326,29 +6350,29 @@
       <c r="L56" s="2">
         <v>1413025</v>
       </c>
-      <c r="M56" s="4" t="s">
+      <c r="M56" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N56" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O56" s="7" t="s">
+      <c r="N56" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O56" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P56" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q56" s="17">
+      <c r="Q56" s="18">
         <v>46155</v>
       </c>
-      <c r="R56" s="18">
+      <c r="R56" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="57" spans="1:18">
-      <c r="A57" s="6" t="s">
+    <row r="57" spans="1:18" hidden="1">
+      <c r="A57" s="7" t="s">
         <v>134</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -6384,29 +6408,29 @@
       <c r="L57" s="2">
         <v>33226</v>
       </c>
-      <c r="M57" s="4" t="s">
+      <c r="M57" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N57" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O57" s="7" t="s">
+      <c r="N57" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O57" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P57" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q57" s="17">
+      <c r="Q57" s="18">
         <v>46155</v>
       </c>
-      <c r="R57" s="18">
+      <c r="R57" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="58" spans="1:18">
-      <c r="A58" s="6" t="s">
+    <row r="58" spans="1:18" hidden="1">
+      <c r="A58" s="7" t="s">
         <v>136</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -6442,29 +6466,29 @@
       <c r="L58" s="2">
         <v>62943</v>
       </c>
-      <c r="M58" s="4" t="s">
+      <c r="M58" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N58" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O58" s="7" t="s">
+      <c r="N58" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O58" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P58" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q58" s="17">
+      <c r="Q58" s="18">
         <v>46155</v>
       </c>
-      <c r="R58" s="18">
+      <c r="R58" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="59" spans="1:18">
-      <c r="A59" s="6" t="s">
+    <row r="59" spans="1:18" hidden="1">
+      <c r="A59" s="7" t="s">
         <v>138</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -6500,29 +6524,29 @@
       <c r="L59" s="2">
         <v>170062</v>
       </c>
-      <c r="M59" s="4" t="s">
+      <c r="M59" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N59" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O59" s="7" t="s">
+      <c r="N59" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O59" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P59" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q59" s="17">
+      <c r="Q59" s="18">
         <v>46155</v>
       </c>
-      <c r="R59" s="18">
+      <c r="R59" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="60" spans="1:18">
-      <c r="A60" s="6" t="s">
+    <row r="60" spans="1:18" hidden="1">
+      <c r="A60" s="7" t="s">
         <v>140</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -6558,29 +6582,29 @@
       <c r="L60" s="2">
         <v>24520</v>
       </c>
-      <c r="M60" s="4" t="s">
+      <c r="M60" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N60" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O60" s="7" t="s">
+      <c r="N60" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O60" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P60" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q60" s="17">
+      <c r="Q60" s="18">
         <v>46155</v>
       </c>
-      <c r="R60" s="18">
+      <c r="R60" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="61" spans="1:18">
-      <c r="A61" s="6" t="s">
+    <row r="61" spans="1:18" hidden="1">
+      <c r="A61" s="7" t="s">
         <v>141</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -6616,29 +6640,29 @@
       <c r="L61" s="2">
         <v>73227</v>
       </c>
-      <c r="M61" s="4" t="s">
+      <c r="M61" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N61" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O61" s="7" t="s">
+      <c r="N61" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O61" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P61" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q61" s="17">
+      <c r="Q61" s="18">
         <v>46155</v>
       </c>
-      <c r="R61" s="18">
+      <c r="R61" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="62" spans="1:18">
-      <c r="A62" s="6" t="s">
+    <row r="62" spans="1:18" hidden="1">
+      <c r="A62" s="7" t="s">
         <v>143</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -6674,29 +6698,29 @@
       <c r="L62" s="2">
         <v>74106</v>
       </c>
-      <c r="M62" s="4" t="s">
+      <c r="M62" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N62" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O62" s="7" t="s">
+      <c r="N62" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O62" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P62" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q62" s="17">
+      <c r="Q62" s="18">
         <v>46155</v>
       </c>
-      <c r="R62" s="18">
+      <c r="R62" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="63" spans="1:18">
-      <c r="A63" s="6" t="s">
+    <row r="63" spans="1:18" hidden="1">
+      <c r="A63" s="7" t="s">
         <v>145</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -6732,29 +6756,29 @@
       <c r="L63" s="2">
         <v>112224</v>
       </c>
-      <c r="M63" s="4" t="s">
+      <c r="M63" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N63" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O63" s="7" t="s">
+      <c r="N63" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O63" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P63" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q63" s="17">
+      <c r="Q63" s="18">
         <v>46155</v>
       </c>
-      <c r="R63" s="18">
+      <c r="R63" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="64" spans="1:18">
-      <c r="A64" s="6" t="s">
+    <row r="64" spans="1:18" hidden="1">
+      <c r="A64" s="7" t="s">
         <v>147</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -6790,29 +6814,29 @@
       <c r="L64" s="2">
         <v>25341</v>
       </c>
-      <c r="M64" s="4" t="s">
+      <c r="M64" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N64" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O64" s="7" t="s">
+      <c r="N64" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O64" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P64" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q64" s="17">
+      <c r="Q64" s="18">
         <v>46155</v>
       </c>
-      <c r="R64" s="18">
+      <c r="R64" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="65" spans="1:18">
-      <c r="A65" s="6" t="s">
+    <row r="65" spans="1:18" hidden="1">
+      <c r="A65" s="7" t="s">
         <v>149</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -6848,29 +6872,29 @@
       <c r="L65" s="2">
         <v>121518</v>
       </c>
-      <c r="M65" s="4" t="s">
+      <c r="M65" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N65" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O65" s="7" t="s">
+      <c r="N65" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O65" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P65" s="1" t="str">
         <f t="shared" si="0"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q65" s="17">
+      <c r="Q65" s="18">
         <v>46155</v>
       </c>
-      <c r="R65" s="18">
+      <c r="R65" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="66" spans="1:18">
-      <c r="A66" s="6" t="s">
+    <row r="66" spans="1:18" hidden="1">
+      <c r="A66" s="7" t="s">
         <v>151</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -6906,29 +6930,29 @@
       <c r="L66" s="2">
         <v>133301</v>
       </c>
-      <c r="M66" s="4" t="s">
+      <c r="M66" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N66" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O66" s="7" t="s">
+      <c r="N66" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O66" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P66" s="1" t="str">
         <f t="shared" ref="P66:P129" si="1">LEFT(M66,FIND("_",M66)-1)</f>
         <v>13/05/2026</v>
       </c>
-      <c r="Q66" s="17">
+      <c r="Q66" s="18">
         <v>46155</v>
       </c>
-      <c r="R66" s="18">
+      <c r="R66" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="67" spans="1:18">
-      <c r="A67" s="6" t="s">
+    <row r="67" spans="1:18" hidden="1">
+      <c r="A67" s="7" t="s">
         <v>153</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -6964,29 +6988,29 @@
       <c r="L67" s="2">
         <v>62973</v>
       </c>
-      <c r="M67" s="4" t="s">
+      <c r="M67" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N67" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O67" s="7" t="s">
+      <c r="N67" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O67" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P67" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q67" s="17">
+      <c r="Q67" s="18">
         <v>46155</v>
       </c>
-      <c r="R67" s="18">
+      <c r="R67" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="68" spans="1:18">
-      <c r="A68" s="6" t="s">
+    <row r="68" spans="1:18" hidden="1">
+      <c r="A68" s="7" t="s">
         <v>155</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -7022,29 +7046,29 @@
       <c r="L68" s="2">
         <v>46016</v>
       </c>
-      <c r="M68" s="4" t="s">
+      <c r="M68" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N68" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O68" s="7" t="s">
+      <c r="N68" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O68" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P68" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q68" s="17">
+      <c r="Q68" s="18">
         <v>46155</v>
       </c>
-      <c r="R68" s="18">
+      <c r="R68" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="69" spans="1:18">
-      <c r="A69" s="6" t="s">
+    <row r="69" spans="1:18" hidden="1">
+      <c r="A69" s="7" t="s">
         <v>157</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -7080,29 +7104,29 @@
       <c r="L69" s="2">
         <v>52844</v>
       </c>
-      <c r="M69" s="4" t="s">
+      <c r="M69" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N69" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O69" s="7" t="s">
+      <c r="N69" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O69" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P69" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q69" s="17">
+      <c r="Q69" s="18">
         <v>46155</v>
       </c>
-      <c r="R69" s="18">
+      <c r="R69" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="70" spans="1:18">
-      <c r="A70" s="6" t="s">
+    <row r="70" spans="1:18" hidden="1">
+      <c r="A70" s="7" t="s">
         <v>159</v>
       </c>
       <c r="B70" s="1" t="s">
@@ -7138,29 +7162,29 @@
       <c r="L70" s="2">
         <v>247863</v>
       </c>
-      <c r="M70" s="4" t="s">
+      <c r="M70" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N70" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O70" s="7" t="s">
+      <c r="N70" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O70" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P70" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q70" s="17">
+      <c r="Q70" s="18">
         <v>46155</v>
       </c>
-      <c r="R70" s="18">
+      <c r="R70" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="71" spans="1:18">
-      <c r="A71" s="6" t="s">
+    <row r="71" spans="1:18" hidden="1">
+      <c r="A71" s="7" t="s">
         <v>161</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -7196,29 +7220,29 @@
       <c r="L71" s="2">
         <v>66096</v>
       </c>
-      <c r="M71" s="4" t="s">
+      <c r="M71" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N71" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O71" s="7" t="s">
+      <c r="N71" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O71" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P71" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q71" s="17">
+      <c r="Q71" s="18">
         <v>46155</v>
       </c>
-      <c r="R71" s="18">
+      <c r="R71" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="72" spans="1:18">
-      <c r="A72" s="6" t="s">
+    <row r="72" spans="1:18" hidden="1">
+      <c r="A72" s="7" t="s">
         <v>163</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -7254,29 +7278,29 @@
       <c r="L72" s="2">
         <v>244244</v>
       </c>
-      <c r="M72" s="4" t="s">
+      <c r="M72" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N72" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O72" s="7" t="s">
+      <c r="N72" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O72" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P72" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q72" s="17">
+      <c r="Q72" s="18">
         <v>46155</v>
       </c>
-      <c r="R72" s="18">
+      <c r="R72" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="73" spans="1:18">
-      <c r="A73" s="6" t="s">
+    <row r="73" spans="1:18" hidden="1">
+      <c r="A73" s="7" t="s">
         <v>174</v>
       </c>
       <c r="B73" s="1" t="s">
@@ -7312,29 +7336,29 @@
       <c r="L73" s="2">
         <v>275000</v>
       </c>
-      <c r="M73" s="4" t="s">
+      <c r="M73" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N73" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O73" s="7" t="s">
+      <c r="N73" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O73" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P73" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q73" s="17">
+      <c r="Q73" s="18">
         <v>46155</v>
       </c>
-      <c r="R73" s="18">
+      <c r="R73" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="74" spans="1:18">
-      <c r="A74" s="6" t="s">
+    <row r="74" spans="1:18" hidden="1">
+      <c r="A74" s="7" t="s">
         <v>176</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -7370,29 +7394,29 @@
       <c r="L74" s="2">
         <v>147980</v>
       </c>
-      <c r="M74" s="4" t="s">
+      <c r="M74" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N74" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O74" s="7" t="s">
+      <c r="N74" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O74" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P74" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q74" s="17">
+      <c r="Q74" s="18">
         <v>46155</v>
       </c>
-      <c r="R74" s="18">
+      <c r="R74" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="75" spans="1:18">
-      <c r="A75" s="6" t="s">
+    <row r="75" spans="1:18" hidden="1">
+      <c r="A75" s="7" t="s">
         <v>181</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -7428,29 +7452,29 @@
       <c r="L75" s="2">
         <v>221957</v>
       </c>
-      <c r="M75" s="4" t="s">
+      <c r="M75" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N75" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O75" s="7" t="s">
+      <c r="N75" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O75" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P75" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q75" s="17">
+      <c r="Q75" s="18">
         <v>46155</v>
       </c>
-      <c r="R75" s="18">
+      <c r="R75" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="76" spans="1:18">
-      <c r="A76" s="6" t="s">
+    <row r="76" spans="1:18" hidden="1">
+      <c r="A76" s="7" t="s">
         <v>185</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -7486,29 +7510,29 @@
       <c r="L76" s="2">
         <v>52325</v>
       </c>
-      <c r="M76" s="4" t="s">
+      <c r="M76" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N76" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O76" s="7" t="s">
+      <c r="N76" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O76" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P76" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q76" s="17">
+      <c r="Q76" s="18">
         <v>46155</v>
       </c>
-      <c r="R76" s="18">
+      <c r="R76" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="77" spans="1:18">
-      <c r="A77" s="6" t="s">
+    <row r="77" spans="1:18" hidden="1">
+      <c r="A77" s="7" t="s">
         <v>187</v>
       </c>
       <c r="B77" s="1" t="s">
@@ -7544,29 +7568,29 @@
       <c r="L77" s="2">
         <v>151443</v>
       </c>
-      <c r="M77" s="4" t="s">
+      <c r="M77" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N77" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O77" s="7" t="s">
+      <c r="N77" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O77" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P77" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q77" s="17">
+      <c r="Q77" s="18">
         <v>46155</v>
       </c>
-      <c r="R77" s="18">
+      <c r="R77" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="78" spans="1:18">
-      <c r="A78" s="6" t="s">
+    <row r="78" spans="1:18" hidden="1">
+      <c r="A78" s="7" t="s">
         <v>201</v>
       </c>
       <c r="B78" s="1" t="s">
@@ -7602,29 +7626,29 @@
       <c r="L78" s="2">
         <v>100982</v>
       </c>
-      <c r="M78" s="4" t="s">
+      <c r="M78" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N78" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O78" s="7" t="s">
+      <c r="N78" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O78" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P78" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q78" s="17">
+      <c r="Q78" s="18">
         <v>46155</v>
       </c>
-      <c r="R78" s="18">
+      <c r="R78" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="79" spans="1:18">
-      <c r="A79" s="6" t="s">
+    <row r="79" spans="1:18" hidden="1">
+      <c r="A79" s="7" t="s">
         <v>215</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -7660,29 +7684,29 @@
       <c r="L79" s="2">
         <v>75567</v>
       </c>
-      <c r="M79" s="4" t="s">
+      <c r="M79" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N79" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O79" s="7" t="s">
+      <c r="N79" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O79" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P79" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q79" s="17">
+      <c r="Q79" s="18">
         <v>46155</v>
       </c>
-      <c r="R79" s="18">
+      <c r="R79" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="80" spans="1:18">
-      <c r="A80" s="6" t="s">
+    <row r="80" spans="1:18" hidden="1">
+      <c r="A80" s="7" t="s">
         <v>217</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -7718,29 +7742,29 @@
       <c r="L80" s="2">
         <v>1406000</v>
       </c>
-      <c r="M80" s="4" t="s">
+      <c r="M80" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N80" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O80" s="7" t="s">
+      <c r="N80" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O80" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P80" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q80" s="17">
+      <c r="Q80" s="18">
         <v>46155</v>
       </c>
-      <c r="R80" s="18">
+      <c r="R80" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="81" spans="1:18">
-      <c r="A81" s="6" t="s">
+    <row r="81" spans="1:18" hidden="1">
+      <c r="A81" s="7" t="s">
         <v>220</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -7776,29 +7800,29 @@
       <c r="L81" s="2">
         <v>570</v>
       </c>
-      <c r="M81" s="4" t="s">
+      <c r="M81" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N81" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O81" s="7" t="s">
+      <c r="N81" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O81" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P81" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q81" s="17">
+      <c r="Q81" s="18">
         <v>46155</v>
       </c>
-      <c r="R81" s="18">
+      <c r="R81" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="82" spans="1:18">
-      <c r="A82" s="6" t="s">
+    <row r="82" spans="1:18" hidden="1">
+      <c r="A82" s="7" t="s">
         <v>225</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -7834,29 +7858,29 @@
       <c r="L82" s="2">
         <v>44160</v>
       </c>
-      <c r="M82" s="4" t="s">
+      <c r="M82" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N82" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O82" s="7" t="s">
+      <c r="N82" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O82" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P82" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q82" s="17">
+      <c r="Q82" s="18">
         <v>46155</v>
       </c>
-      <c r="R82" s="18">
+      <c r="R82" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="83" spans="1:18">
-      <c r="A83" s="6" t="s">
+    <row r="83" spans="1:18" hidden="1">
+      <c r="A83" s="7" t="s">
         <v>226</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -7892,29 +7916,29 @@
       <c r="L83" s="2">
         <v>454196</v>
       </c>
-      <c r="M83" s="4" t="s">
+      <c r="M83" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N83" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O83" s="7" t="s">
+      <c r="N83" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O83" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P83" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q83" s="17">
+      <c r="Q83" s="18">
         <v>46155</v>
       </c>
-      <c r="R83" s="18">
+      <c r="R83" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="84" spans="1:18">
-      <c r="A84" s="6" t="s">
+    <row r="84" spans="1:18" hidden="1">
+      <c r="A84" s="7" t="s">
         <v>228</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -7950,29 +7974,29 @@
       <c r="L84" s="2">
         <v>106487</v>
       </c>
-      <c r="M84" s="4" t="s">
+      <c r="M84" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N84" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O84" s="7" t="s">
+      <c r="N84" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O84" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P84" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q84" s="17">
+      <c r="Q84" s="18">
         <v>46155</v>
       </c>
-      <c r="R84" s="18">
+      <c r="R84" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="85" spans="1:18">
-      <c r="A85" s="6" t="s">
+    <row r="85" spans="1:18" hidden="1">
+      <c r="A85" s="7" t="s">
         <v>230</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -8008,29 +8032,29 @@
       <c r="L85" s="2">
         <v>212047</v>
       </c>
-      <c r="M85" s="4" t="s">
+      <c r="M85" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N85" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O85" s="7" t="s">
+      <c r="N85" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O85" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P85" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q85" s="17">
+      <c r="Q85" s="18">
         <v>46155</v>
       </c>
-      <c r="R85" s="18">
+      <c r="R85" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="86" spans="1:18">
-      <c r="A86" s="6" t="s">
+    <row r="86" spans="1:18" hidden="1">
+      <c r="A86" s="7" t="s">
         <v>233</v>
       </c>
       <c r="B86" s="1" t="s">
@@ -8066,29 +8090,29 @@
       <c r="L86" s="2">
         <v>89450</v>
       </c>
-      <c r="M86" s="4" t="s">
+      <c r="M86" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N86" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O86" s="7" t="s">
+      <c r="N86" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O86" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P86" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q86" s="17">
+      <c r="Q86" s="18">
         <v>46155</v>
       </c>
-      <c r="R86" s="18">
+      <c r="R86" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="87" spans="1:18">
-      <c r="A87" s="6" t="s">
+    <row r="87" spans="1:18" hidden="1">
+      <c r="A87" s="7" t="s">
         <v>277</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -8124,29 +8148,29 @@
       <c r="L87" s="2">
         <v>32930</v>
       </c>
-      <c r="M87" s="4" t="s">
+      <c r="M87" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N87" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O87" s="7" t="s">
+      <c r="N87" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O87" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P87" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q87" s="17">
+      <c r="Q87" s="18">
         <v>46155</v>
       </c>
-      <c r="R87" s="18">
+      <c r="R87" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="88" spans="1:18">
-      <c r="A88" s="6" t="s">
+    <row r="88" spans="1:18" hidden="1">
+      <c r="A88" s="7" t="s">
         <v>283</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -8182,29 +8206,29 @@
       <c r="L88" s="2">
         <v>37767</v>
       </c>
-      <c r="M88" s="4" t="s">
+      <c r="M88" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N88" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O88" s="7" t="s">
+      <c r="N88" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O88" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P88" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q88" s="17">
+      <c r="Q88" s="18">
         <v>46155</v>
       </c>
-      <c r="R88" s="18">
+      <c r="R88" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="89" spans="1:18">
-      <c r="A89" s="6" t="s">
+    <row r="89" spans="1:18" hidden="1">
+      <c r="A89" s="7" t="s">
         <v>285</v>
       </c>
       <c r="B89" s="1" t="s">
@@ -8240,29 +8264,29 @@
       <c r="L89" s="2">
         <v>29646</v>
       </c>
-      <c r="M89" s="4" t="s">
+      <c r="M89" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N89" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O89" s="7" t="s">
+      <c r="N89" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O89" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P89" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q89" s="17">
+      <c r="Q89" s="18">
         <v>46155</v>
       </c>
-      <c r="R89" s="18">
+      <c r="R89" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="90" spans="1:18">
-      <c r="A90" s="6" t="s">
+    <row r="90" spans="1:18" hidden="1">
+      <c r="A90" s="7" t="s">
         <v>288</v>
       </c>
       <c r="B90" s="1" t="s">
@@ -8298,29 +8322,29 @@
       <c r="L90" s="2">
         <v>28725</v>
       </c>
-      <c r="M90" s="4" t="s">
+      <c r="M90" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N90" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O90" s="7" t="s">
+      <c r="N90" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O90" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P90" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q90" s="17">
+      <c r="Q90" s="18">
         <v>46155</v>
       </c>
-      <c r="R90" s="18">
+      <c r="R90" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="91" spans="1:18">
-      <c r="A91" s="6" t="s">
+    <row r="91" spans="1:18" hidden="1">
+      <c r="A91" s="7" t="s">
         <v>290</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -8356,29 +8380,29 @@
       <c r="L91" s="2">
         <v>98436</v>
       </c>
-      <c r="M91" s="4" t="s">
+      <c r="M91" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N91" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O91" s="7" t="s">
+      <c r="N91" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O91" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P91" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q91" s="17">
+      <c r="Q91" s="18">
         <v>46155</v>
       </c>
-      <c r="R91" s="18">
+      <c r="R91" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="92" spans="1:18">
-      <c r="A92" s="6" t="s">
+    <row r="92" spans="1:18" hidden="1">
+      <c r="A92" s="7" t="s">
         <v>291</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -8414,29 +8438,29 @@
       <c r="L92" s="2">
         <v>77520</v>
       </c>
-      <c r="M92" s="4" t="s">
+      <c r="M92" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N92" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O92" s="7" t="s">
+      <c r="N92" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O92" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P92" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q92" s="17">
+      <c r="Q92" s="18">
         <v>46155</v>
       </c>
-      <c r="R92" s="18">
+      <c r="R92" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="93" spans="1:18">
-      <c r="A93" s="6" t="s">
+    <row r="93" spans="1:18" hidden="1">
+      <c r="A93" s="7" t="s">
         <v>293</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -8472,29 +8496,29 @@
       <c r="L93" s="2">
         <v>91729</v>
       </c>
-      <c r="M93" s="4" t="s">
+      <c r="M93" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N93" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O93" s="7" t="s">
+      <c r="N93" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O93" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P93" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q93" s="17">
+      <c r="Q93" s="18">
         <v>46155</v>
       </c>
-      <c r="R93" s="18">
+      <c r="R93" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="94" spans="1:18">
-      <c r="A94" s="6" t="s">
+    <row r="94" spans="1:18" hidden="1">
+      <c r="A94" s="7" t="s">
         <v>295</v>
       </c>
       <c r="B94" s="1" t="s">
@@ -8530,29 +8554,29 @@
       <c r="L94" s="2">
         <v>901074</v>
       </c>
-      <c r="M94" s="4" t="s">
+      <c r="M94" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N94" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O94" s="7" t="s">
+      <c r="N94" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O94" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P94" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q94" s="17">
+      <c r="Q94" s="18">
         <v>46155</v>
       </c>
-      <c r="R94" s="18">
+      <c r="R94" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="95" spans="1:18">
-      <c r="A95" s="6" t="s">
+    <row r="95" spans="1:18" hidden="1">
+      <c r="A95" s="7" t="s">
         <v>299</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -8588,29 +8612,29 @@
       <c r="L95" s="2">
         <v>163982</v>
       </c>
-      <c r="M95" s="4" t="s">
+      <c r="M95" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N95" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O95" s="7" t="s">
+      <c r="N95" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O95" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P95" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q95" s="17">
+      <c r="Q95" s="18">
         <v>46155</v>
       </c>
-      <c r="R95" s="18">
+      <c r="R95" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="96" spans="1:18">
-      <c r="A96" s="6" t="s">
+    <row r="96" spans="1:18" hidden="1">
+      <c r="A96" s="7" t="s">
         <v>301</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -8646,29 +8670,29 @@
       <c r="L96" s="2">
         <v>38315</v>
       </c>
-      <c r="M96" s="4" t="s">
+      <c r="M96" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N96" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O96" s="7" t="s">
+      <c r="N96" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O96" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P96" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q96" s="17">
+      <c r="Q96" s="18">
         <v>46155</v>
       </c>
-      <c r="R96" s="18">
+      <c r="R96" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="97" spans="1:18">
-      <c r="A97" s="6" t="s">
+    <row r="97" spans="1:18" hidden="1">
+      <c r="A97" s="7" t="s">
         <v>303</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -8704,29 +8728,29 @@
       <c r="L97" s="2">
         <v>113195</v>
       </c>
-      <c r="M97" s="4" t="s">
+      <c r="M97" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N97" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O97" s="7" t="s">
+      <c r="N97" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O97" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P97" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q97" s="17">
+      <c r="Q97" s="18">
         <v>46155</v>
       </c>
-      <c r="R97" s="18">
+      <c r="R97" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="98" spans="1:18">
-      <c r="A98" s="6" t="s">
+    <row r="98" spans="1:18" hidden="1">
+      <c r="A98" s="7" t="s">
         <v>304</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -8762,29 +8786,29 @@
       <c r="L98" s="2">
         <v>82788</v>
       </c>
-      <c r="M98" s="4" t="s">
+      <c r="M98" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N98" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O98" s="7" t="s">
+      <c r="N98" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O98" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P98" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q98" s="17">
+      <c r="Q98" s="18">
         <v>46155</v>
       </c>
-      <c r="R98" s="18">
+      <c r="R98" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="99" spans="1:18">
-      <c r="A99" s="6" t="s">
+    <row r="99" spans="1:18" hidden="1">
+      <c r="A99" s="7" t="s">
         <v>306</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -8820,29 +8844,29 @@
       <c r="L99" s="2">
         <v>108528</v>
       </c>
-      <c r="M99" s="4" t="s">
+      <c r="M99" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N99" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O99" s="7" t="s">
+      <c r="N99" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O99" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P99" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q99" s="17">
+      <c r="Q99" s="18">
         <v>46155</v>
       </c>
-      <c r="R99" s="18">
+      <c r="R99" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="100" spans="1:18">
-      <c r="A100" s="6" t="s">
+    <row r="100" spans="1:18" hidden="1">
+      <c r="A100" s="7" t="s">
         <v>307</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -8878,29 +8902,29 @@
       <c r="L100" s="2">
         <v>91549</v>
       </c>
-      <c r="M100" s="4" t="s">
+      <c r="M100" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N100" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O100" s="7" t="s">
+      <c r="N100" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O100" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P100" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q100" s="17">
+      <c r="Q100" s="18">
         <v>46155</v>
       </c>
-      <c r="R100" s="18">
+      <c r="R100" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="101" spans="1:18">
-      <c r="A101" s="6" t="s">
+    <row r="101" spans="1:18" hidden="1">
+      <c r="A101" s="7" t="s">
         <v>308</v>
       </c>
       <c r="B101" s="1" t="s">
@@ -8936,29 +8960,29 @@
       <c r="L101" s="2">
         <v>86299</v>
       </c>
-      <c r="M101" s="4" t="s">
+      <c r="M101" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N101" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O101" s="7" t="s">
+      <c r="N101" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O101" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P101" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q101" s="17">
+      <c r="Q101" s="18">
         <v>46155</v>
       </c>
-      <c r="R101" s="18">
+      <c r="R101" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="102" spans="1:18">
-      <c r="A102" s="6" t="s">
+    <row r="102" spans="1:18" hidden="1">
+      <c r="A102" s="7" t="s">
         <v>310</v>
       </c>
       <c r="B102" s="1" t="s">
@@ -8994,29 +9018,29 @@
       <c r="L102" s="2">
         <v>181242</v>
       </c>
-      <c r="M102" s="4" t="s">
+      <c r="M102" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N102" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O102" s="7" t="s">
+      <c r="N102" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O102" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P102" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q102" s="17">
+      <c r="Q102" s="18">
         <v>46155</v>
       </c>
-      <c r="R102" s="18">
+      <c r="R102" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="103" spans="1:18">
-      <c r="A103" s="6" t="s">
+    <row r="103" spans="1:18" hidden="1">
+      <c r="A103" s="7" t="s">
         <v>313</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -9052,29 +9076,29 @@
       <c r="L103" s="2">
         <v>78385</v>
       </c>
-      <c r="M103" s="4" t="s">
+      <c r="M103" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N103" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O103" s="7" t="s">
+      <c r="N103" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O103" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P103" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q103" s="17">
+      <c r="Q103" s="18">
         <v>46155</v>
       </c>
-      <c r="R103" s="18">
+      <c r="R103" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="104" spans="1:18">
-      <c r="A104" s="6" t="s">
+    <row r="104" spans="1:18" hidden="1">
+      <c r="A104" s="7" t="s">
         <v>315</v>
       </c>
       <c r="B104" s="1" t="s">
@@ -9110,29 +9134,29 @@
       <c r="L104" s="2">
         <v>77604</v>
       </c>
-      <c r="M104" s="4" t="s">
+      <c r="M104" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N104" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O104" s="7" t="s">
+      <c r="N104" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O104" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P104" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q104" s="17">
+      <c r="Q104" s="18">
         <v>46155</v>
       </c>
-      <c r="R104" s="18">
+      <c r="R104" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="105" spans="1:18">
-      <c r="A105" s="6" t="s">
+    <row r="105" spans="1:18" hidden="1">
+      <c r="A105" s="7" t="s">
         <v>316</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -9168,29 +9192,29 @@
       <c r="L105" s="2">
         <v>106741</v>
       </c>
-      <c r="M105" s="4" t="s">
+      <c r="M105" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N105" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O105" s="7" t="s">
+      <c r="N105" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O105" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P105" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q105" s="17">
+      <c r="Q105" s="18">
         <v>46155</v>
       </c>
-      <c r="R105" s="18">
+      <c r="R105" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="106" spans="1:18">
-      <c r="A106" s="6" t="s">
+    <row r="106" spans="1:18" hidden="1">
+      <c r="A106" s="7" t="s">
         <v>318</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -9226,29 +9250,29 @@
       <c r="L106" s="2">
         <v>120031</v>
       </c>
-      <c r="M106" s="4" t="s">
+      <c r="M106" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N106" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O106" s="7" t="s">
+      <c r="N106" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O106" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P106" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q106" s="17">
+      <c r="Q106" s="18">
         <v>46155</v>
       </c>
-      <c r="R106" s="18">
+      <c r="R106" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="107" spans="1:18">
-      <c r="A107" s="6" t="s">
+    <row r="107" spans="1:18" hidden="1">
+      <c r="A107" s="7" t="s">
         <v>319</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -9284,29 +9308,29 @@
       <c r="L107" s="2">
         <v>37427</v>
       </c>
-      <c r="M107" s="4" t="s">
+      <c r="M107" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N107" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O107" s="7" t="s">
+      <c r="N107" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O107" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P107" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q107" s="17">
+      <c r="Q107" s="18">
         <v>46155</v>
       </c>
-      <c r="R107" s="18">
+      <c r="R107" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="108" spans="1:18">
-      <c r="A108" s="6" t="s">
+    <row r="108" spans="1:18" hidden="1">
+      <c r="A108" s="7" t="s">
         <v>320</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -9342,29 +9366,29 @@
       <c r="L108" s="2">
         <v>406401</v>
       </c>
-      <c r="M108" s="4" t="s">
+      <c r="M108" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N108" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O108" s="7" t="s">
+      <c r="N108" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O108" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P108" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q108" s="17">
+      <c r="Q108" s="18">
         <v>46155</v>
       </c>
-      <c r="R108" s="18">
+      <c r="R108" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="109" spans="1:18">
-      <c r="A109" s="6" t="s">
+    <row r="109" spans="1:18" hidden="1">
+      <c r="A109" s="7" t="s">
         <v>322</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -9400,29 +9424,29 @@
       <c r="L109" s="2">
         <v>64502</v>
       </c>
-      <c r="M109" s="4" t="s">
+      <c r="M109" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N109" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O109" s="7" t="s">
+      <c r="N109" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O109" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P109" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q109" s="17">
+      <c r="Q109" s="18">
         <v>46155</v>
       </c>
-      <c r="R109" s="18">
+      <c r="R109" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="110" spans="1:18">
-      <c r="A110" s="6" t="s">
+    <row r="110" spans="1:18" hidden="1">
+      <c r="A110" s="7" t="s">
         <v>324</v>
       </c>
       <c r="B110" s="1" t="s">
@@ -9458,29 +9482,29 @@
       <c r="L110" s="2">
         <v>72984</v>
       </c>
-      <c r="M110" s="4" t="s">
+      <c r="M110" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N110" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O110" s="7" t="s">
+      <c r="N110" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O110" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P110" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q110" s="17">
+      <c r="Q110" s="18">
         <v>46155</v>
       </c>
-      <c r="R110" s="18">
+      <c r="R110" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="111" spans="1:18">
-      <c r="A111" s="6" t="s">
+    <row r="111" spans="1:18" hidden="1">
+      <c r="A111" s="7" t="s">
         <v>325</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -9516,29 +9540,29 @@
       <c r="L111" s="2">
         <v>54181</v>
       </c>
-      <c r="M111" s="4" t="s">
+      <c r="M111" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N111" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O111" s="7" t="s">
+      <c r="N111" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O111" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P111" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q111" s="17">
+      <c r="Q111" s="18">
         <v>46155</v>
       </c>
-      <c r="R111" s="18">
+      <c r="R111" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="112" spans="1:18">
-      <c r="A112" s="6" t="s">
+    <row r="112" spans="1:18" hidden="1">
+      <c r="A112" s="7" t="s">
         <v>326</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -9574,29 +9598,29 @@
       <c r="L112" s="2">
         <v>45450</v>
       </c>
-      <c r="M112" s="4" t="s">
+      <c r="M112" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N112" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O112" s="7" t="s">
+      <c r="N112" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O112" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P112" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q112" s="17">
+      <c r="Q112" s="18">
         <v>46155</v>
       </c>
-      <c r="R112" s="18">
+      <c r="R112" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="113" spans="1:18">
-      <c r="A113" s="6" t="s">
+    <row r="113" spans="1:18" hidden="1">
+      <c r="A113" s="7" t="s">
         <v>327</v>
       </c>
       <c r="B113" s="1" t="s">
@@ -9632,29 +9656,29 @@
       <c r="L113" s="2">
         <v>73801</v>
       </c>
-      <c r="M113" s="4" t="s">
+      <c r="M113" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N113" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O113" s="7" t="s">
+      <c r="N113" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O113" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P113" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q113" s="17">
+      <c r="Q113" s="18">
         <v>46155</v>
       </c>
-      <c r="R113" s="18">
+      <c r="R113" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="114" spans="1:18">
-      <c r="A114" s="6" t="s">
+    <row r="114" spans="1:18" hidden="1">
+      <c r="A114" s="7" t="s">
         <v>328</v>
       </c>
       <c r="B114" s="1" t="s">
@@ -9690,29 +9714,29 @@
       <c r="L114" s="2">
         <v>63533</v>
       </c>
-      <c r="M114" s="4" t="s">
+      <c r="M114" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N114" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O114" s="7" t="s">
+      <c r="N114" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O114" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P114" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q114" s="17">
+      <c r="Q114" s="18">
         <v>46155</v>
       </c>
-      <c r="R114" s="18">
+      <c r="R114" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="115" spans="1:18">
-      <c r="A115" s="6" t="s">
+    <row r="115" spans="1:18" hidden="1">
+      <c r="A115" s="7" t="s">
         <v>329</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -9748,29 +9772,29 @@
       <c r="L115" s="2">
         <v>74776</v>
       </c>
-      <c r="M115" s="4" t="s">
+      <c r="M115" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N115" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O115" s="7" t="s">
+      <c r="N115" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O115" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P115" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q115" s="17">
+      <c r="Q115" s="18">
         <v>46155</v>
       </c>
-      <c r="R115" s="18">
+      <c r="R115" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="116" spans="1:18">
-      <c r="A116" s="6" t="s">
+    <row r="116" spans="1:18" hidden="1">
+      <c r="A116" s="7" t="s">
         <v>330</v>
       </c>
       <c r="B116" s="1" t="s">
@@ -9806,29 +9830,29 @@
       <c r="L116" s="2">
         <v>118723</v>
       </c>
-      <c r="M116" s="4" t="s">
+      <c r="M116" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N116" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O116" s="7" t="s">
+      <c r="N116" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O116" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P116" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q116" s="17">
+      <c r="Q116" s="18">
         <v>46155</v>
       </c>
-      <c r="R116" s="18">
+      <c r="R116" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="117" spans="1:18">
-      <c r="A117" s="6" t="s">
+    <row r="117" spans="1:18" hidden="1">
+      <c r="A117" s="7" t="s">
         <v>332</v>
       </c>
       <c r="B117" s="1" t="s">
@@ -9864,29 +9888,29 @@
       <c r="L117" s="2">
         <v>86721</v>
       </c>
-      <c r="M117" s="4" t="s">
+      <c r="M117" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N117" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O117" s="7" t="s">
+      <c r="N117" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O117" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P117" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q117" s="17">
+      <c r="Q117" s="18">
         <v>46155</v>
       </c>
-      <c r="R117" s="18">
+      <c r="R117" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="118" spans="1:18">
-      <c r="A118" s="6" t="s">
+    <row r="118" spans="1:18" hidden="1">
+      <c r="A118" s="7" t="s">
         <v>333</v>
       </c>
       <c r="B118" s="1" t="s">
@@ -9922,29 +9946,29 @@
       <c r="L118" s="2">
         <v>74882</v>
       </c>
-      <c r="M118" s="4" t="s">
+      <c r="M118" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N118" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O118" s="7" t="s">
+      <c r="N118" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O118" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P118" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q118" s="17">
+      <c r="Q118" s="18">
         <v>46155</v>
       </c>
-      <c r="R118" s="18">
+      <c r="R118" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="119" spans="1:18">
-      <c r="A119" s="6" t="s">
+    <row r="119" spans="1:18" hidden="1">
+      <c r="A119" s="7" t="s">
         <v>334</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -9980,29 +10004,29 @@
       <c r="L119" s="2">
         <v>62083</v>
       </c>
-      <c r="M119" s="4" t="s">
+      <c r="M119" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N119" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O119" s="7" t="s">
+      <c r="N119" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O119" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P119" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q119" s="17">
+      <c r="Q119" s="18">
         <v>46155</v>
       </c>
-      <c r="R119" s="18">
+      <c r="R119" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="120" spans="1:18">
-      <c r="A120" s="6" t="s">
+    <row r="120" spans="1:18" hidden="1">
+      <c r="A120" s="7" t="s">
         <v>335</v>
       </c>
       <c r="B120" s="1" t="s">
@@ -10038,29 +10062,29 @@
       <c r="L120" s="2">
         <v>89395</v>
       </c>
-      <c r="M120" s="4" t="s">
+      <c r="M120" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N120" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O120" s="7" t="s">
+      <c r="N120" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O120" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P120" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q120" s="17">
+      <c r="Q120" s="18">
         <v>46155</v>
       </c>
-      <c r="R120" s="18">
+      <c r="R120" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="121" spans="1:18">
-      <c r="A121" s="6" t="s">
+    <row r="121" spans="1:18" hidden="1">
+      <c r="A121" s="7" t="s">
         <v>336</v>
       </c>
       <c r="B121" s="1" t="s">
@@ -10096,29 +10120,29 @@
       <c r="L121" s="2">
         <v>116155</v>
       </c>
-      <c r="M121" s="4" t="s">
+      <c r="M121" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N121" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O121" s="7" t="s">
+      <c r="N121" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O121" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P121" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q121" s="17">
+      <c r="Q121" s="18">
         <v>46155</v>
       </c>
-      <c r="R121" s="18">
+      <c r="R121" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="122" spans="1:18">
-      <c r="A122" s="6" t="s">
+    <row r="122" spans="1:18" hidden="1">
+      <c r="A122" s="7" t="s">
         <v>337</v>
       </c>
       <c r="B122" s="1" t="s">
@@ -10154,29 +10178,29 @@
       <c r="L122" s="2">
         <v>83054</v>
       </c>
-      <c r="M122" s="4" t="s">
+      <c r="M122" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N122" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O122" s="7" t="s">
+      <c r="N122" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O122" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P122" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q122" s="17">
+      <c r="Q122" s="18">
         <v>46155</v>
       </c>
-      <c r="R122" s="18">
+      <c r="R122" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="123" spans="1:18">
-      <c r="A123" s="6" t="s">
+    <row r="123" spans="1:18" hidden="1">
+      <c r="A123" s="7" t="s">
         <v>339</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -10212,29 +10236,29 @@
       <c r="L123" s="2">
         <v>52571</v>
       </c>
-      <c r="M123" s="4" t="s">
+      <c r="M123" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N123" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O123" s="7" t="s">
+      <c r="N123" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O123" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P123" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q123" s="17">
+      <c r="Q123" s="18">
         <v>46155</v>
       </c>
-      <c r="R123" s="18">
+      <c r="R123" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="124" spans="1:18">
-      <c r="A124" s="6" t="s">
+    <row r="124" spans="1:18" hidden="1">
+      <c r="A124" s="7" t="s">
         <v>341</v>
       </c>
       <c r="B124" s="1" t="s">
@@ -10270,29 +10294,29 @@
       <c r="L124" s="2">
         <v>84919</v>
       </c>
-      <c r="M124" s="4" t="s">
+      <c r="M124" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N124" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O124" s="7" t="s">
+      <c r="N124" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O124" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P124" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q124" s="17">
+      <c r="Q124" s="18">
         <v>46155</v>
       </c>
-      <c r="R124" s="18">
+      <c r="R124" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="125" spans="1:18">
-      <c r="A125" s="6" t="s">
+    <row r="125" spans="1:18" hidden="1">
+      <c r="A125" s="7" t="s">
         <v>342</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -10328,29 +10352,29 @@
       <c r="L125" s="2">
         <v>105469</v>
       </c>
-      <c r="M125" s="4" t="s">
+      <c r="M125" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N125" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O125" s="7" t="s">
+      <c r="N125" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O125" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P125" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q125" s="17">
+      <c r="Q125" s="18">
         <v>46155</v>
       </c>
-      <c r="R125" s="18">
+      <c r="R125" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="126" spans="1:18">
-      <c r="A126" s="6" t="s">
+    <row r="126" spans="1:18" hidden="1">
+      <c r="A126" s="7" t="s">
         <v>343</v>
       </c>
       <c r="B126" s="1" t="s">
@@ -10386,29 +10410,29 @@
       <c r="L126" s="2">
         <v>65143</v>
       </c>
-      <c r="M126" s="4" t="s">
+      <c r="M126" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N126" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O126" s="7" t="s">
+      <c r="N126" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O126" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P126" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q126" s="17">
+      <c r="Q126" s="18">
         <v>46155</v>
       </c>
-      <c r="R126" s="18">
+      <c r="R126" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="127" spans="1:18">
-      <c r="A127" s="6" t="s">
+    <row r="127" spans="1:18" hidden="1">
+      <c r="A127" s="7" t="s">
         <v>344</v>
       </c>
       <c r="B127" s="1" t="s">
@@ -10444,29 +10468,29 @@
       <c r="L127" s="2">
         <v>62435</v>
       </c>
-      <c r="M127" s="4" t="s">
+      <c r="M127" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N127" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O127" s="7" t="s">
+      <c r="N127" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O127" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P127" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q127" s="17">
+      <c r="Q127" s="18">
         <v>46155</v>
       </c>
-      <c r="R127" s="18">
+      <c r="R127" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="128" spans="1:18">
-      <c r="A128" s="6" t="s">
+    <row r="128" spans="1:18" hidden="1">
+      <c r="A128" s="7" t="s">
         <v>345</v>
       </c>
       <c r="B128" s="1" t="s">
@@ -10502,29 +10526,29 @@
       <c r="L128" s="2">
         <v>49363</v>
       </c>
-      <c r="M128" s="4" t="s">
+      <c r="M128" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N128" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O128" s="7" t="s">
+      <c r="N128" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O128" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P128" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q128" s="17">
+      <c r="Q128" s="18">
         <v>46155</v>
       </c>
-      <c r="R128" s="18">
+      <c r="R128" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="129" spans="1:18">
-      <c r="A129" s="6" t="s">
+    <row r="129" spans="1:18" hidden="1">
+      <c r="A129" s="7" t="s">
         <v>347</v>
       </c>
       <c r="B129" s="1" t="s">
@@ -10560,29 +10584,29 @@
       <c r="L129" s="2">
         <v>133028</v>
       </c>
-      <c r="M129" s="4" t="s">
+      <c r="M129" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N129" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O129" s="7" t="s">
+      <c r="N129" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O129" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P129" s="1" t="str">
         <f t="shared" si="1"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q129" s="17">
+      <c r="Q129" s="18">
         <v>46155</v>
       </c>
-      <c r="R129" s="18">
+      <c r="R129" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="130" spans="1:18">
-      <c r="A130" s="6" t="s">
+    <row r="130" spans="1:18" hidden="1">
+      <c r="A130" s="7" t="s">
         <v>348</v>
       </c>
       <c r="B130" s="1" t="s">
@@ -10618,29 +10642,29 @@
       <c r="L130" s="2">
         <v>587602</v>
       </c>
-      <c r="M130" s="4" t="s">
+      <c r="M130" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N130" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O130" s="7" t="s">
+      <c r="N130" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O130" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P130" s="1" t="str">
-        <f t="shared" ref="P130:P193" si="2">LEFT(M130,FIND("_",M130)-1)</f>
+        <f t="shared" ref="P130:Q193" si="2">LEFT(M130,FIND("_",M130)-1)</f>
         <v>13/05/2026</v>
       </c>
-      <c r="Q130" s="17">
+      <c r="Q130" s="18">
         <v>46155</v>
       </c>
-      <c r="R130" s="18">
+      <c r="R130" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="131" spans="1:18">
-      <c r="A131" s="6" t="s">
+    <row r="131" spans="1:18" hidden="1">
+      <c r="A131" s="7" t="s">
         <v>349</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -10676,29 +10700,29 @@
       <c r="L131" s="2">
         <v>246397</v>
       </c>
-      <c r="M131" s="4" t="s">
+      <c r="M131" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N131" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O131" s="7" t="s">
+      <c r="N131" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O131" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P131" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q131" s="17">
+      <c r="Q131" s="18">
         <v>46155</v>
       </c>
-      <c r="R131" s="18">
+      <c r="R131" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="132" spans="1:18">
-      <c r="A132" s="6" t="s">
+    <row r="132" spans="1:18" hidden="1">
+      <c r="A132" s="7" t="s">
         <v>351</v>
       </c>
       <c r="B132" s="1" t="s">
@@ -10734,29 +10758,29 @@
       <c r="L132" s="2">
         <v>260219</v>
       </c>
-      <c r="M132" s="4" t="s">
+      <c r="M132" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N132" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O132" s="7" t="s">
+      <c r="N132" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O132" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P132" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q132" s="17">
+      <c r="Q132" s="18">
         <v>46155</v>
       </c>
-      <c r="R132" s="18">
+      <c r="R132" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="133" spans="1:18">
-      <c r="A133" s="6" t="s">
+    <row r="133" spans="1:18" hidden="1">
+      <c r="A133" s="7" t="s">
         <v>353</v>
       </c>
       <c r="B133" s="1" t="s">
@@ -10792,29 +10816,29 @@
       <c r="L133" s="2">
         <v>61683</v>
       </c>
-      <c r="M133" s="4" t="s">
+      <c r="M133" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N133" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O133" s="7" t="s">
+      <c r="N133" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O133" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P133" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q133" s="17">
+      <c r="Q133" s="18">
         <v>46155</v>
       </c>
-      <c r="R133" s="18">
+      <c r="R133" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="134" spans="1:18">
-      <c r="A134" s="6" t="s">
+    <row r="134" spans="1:18" hidden="1">
+      <c r="A134" s="7" t="s">
         <v>356</v>
       </c>
       <c r="B134" s="1" t="s">
@@ -10850,29 +10874,29 @@
       <c r="L134" s="2">
         <v>129790</v>
       </c>
-      <c r="M134" s="4" t="s">
+      <c r="M134" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N134" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O134" s="7" t="s">
+      <c r="N134" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O134" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P134" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q134" s="17">
+      <c r="Q134" s="18">
         <v>46155</v>
       </c>
-      <c r="R134" s="18">
+      <c r="R134" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="135" spans="1:18">
-      <c r="A135" s="6" t="s">
+    <row r="135" spans="1:18" hidden="1">
+      <c r="A135" s="7" t="s">
         <v>358</v>
       </c>
       <c r="B135" s="1" t="s">
@@ -10908,29 +10932,29 @@
       <c r="L135" s="2">
         <v>79180</v>
       </c>
-      <c r="M135" s="4" t="s">
+      <c r="M135" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N135" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O135" s="7" t="s">
+      <c r="N135" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O135" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P135" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q135" s="17">
+      <c r="Q135" s="18">
         <v>46155</v>
       </c>
-      <c r="R135" s="18">
+      <c r="R135" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="136" spans="1:18">
-      <c r="A136" s="6" t="s">
+    <row r="136" spans="1:18" hidden="1">
+      <c r="A136" s="7" t="s">
         <v>359</v>
       </c>
       <c r="B136" s="1" t="s">
@@ -10966,29 +10990,29 @@
       <c r="L136" s="2">
         <v>52205</v>
       </c>
-      <c r="M136" s="4" t="s">
+      <c r="M136" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N136" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O136" s="7" t="s">
+      <c r="N136" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O136" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P136" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q136" s="17">
+      <c r="Q136" s="18">
         <v>46155</v>
       </c>
-      <c r="R136" s="18">
+      <c r="R136" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="137" spans="1:18">
-      <c r="A137" s="6" t="s">
+    <row r="137" spans="1:18" hidden="1">
+      <c r="A137" s="7" t="s">
         <v>362</v>
       </c>
       <c r="B137" s="1" t="s">
@@ -11024,29 +11048,29 @@
       <c r="L137" s="2">
         <v>83651</v>
       </c>
-      <c r="M137" s="4" t="s">
+      <c r="M137" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N137" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O137" s="7" t="s">
+      <c r="N137" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O137" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P137" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q137" s="17">
+      <c r="Q137" s="18">
         <v>46155</v>
       </c>
-      <c r="R137" s="18">
+      <c r="R137" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="138" spans="1:18">
-      <c r="A138" s="6" t="s">
+    <row r="138" spans="1:18" hidden="1">
+      <c r="A138" s="7" t="s">
         <v>364</v>
       </c>
       <c r="B138" s="1" t="s">
@@ -11082,29 +11106,29 @@
       <c r="L138" s="2">
         <v>98189</v>
       </c>
-      <c r="M138" s="4" t="s">
+      <c r="M138" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N138" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O138" s="7" t="s">
+      <c r="N138" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O138" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P138" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q138" s="17">
+      <c r="Q138" s="18">
         <v>46155</v>
       </c>
-      <c r="R138" s="18">
+      <c r="R138" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="139" spans="1:18">
-      <c r="A139" s="6" t="s">
+    <row r="139" spans="1:18" hidden="1">
+      <c r="A139" s="7" t="s">
         <v>365</v>
       </c>
       <c r="B139" s="1" t="s">
@@ -11140,29 +11164,29 @@
       <c r="L139" s="2">
         <v>123017</v>
       </c>
-      <c r="M139" s="4" t="s">
+      <c r="M139" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N139" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O139" s="7" t="s">
+      <c r="N139" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O139" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P139" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q139" s="17">
+      <c r="Q139" s="18">
         <v>46155</v>
       </c>
-      <c r="R139" s="18">
+      <c r="R139" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="140" spans="1:18">
-      <c r="A140" s="6" t="s">
+    <row r="140" spans="1:18" hidden="1">
+      <c r="A140" s="7" t="s">
         <v>367</v>
       </c>
       <c r="B140" s="1" t="s">
@@ -11198,29 +11222,29 @@
       <c r="L140" s="2">
         <v>311451</v>
       </c>
-      <c r="M140" s="4" t="s">
+      <c r="M140" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N140" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O140" s="7" t="s">
+      <c r="N140" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O140" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P140" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q140" s="17">
+      <c r="Q140" s="18">
         <v>46155</v>
       </c>
-      <c r="R140" s="18">
+      <c r="R140" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="141" spans="1:18">
-      <c r="A141" s="6" t="s">
+    <row r="141" spans="1:18" hidden="1">
+      <c r="A141" s="7" t="s">
         <v>368</v>
       </c>
       <c r="B141" s="1" t="s">
@@ -11256,29 +11280,29 @@
       <c r="L141" s="2">
         <v>126032</v>
       </c>
-      <c r="M141" s="4" t="s">
+      <c r="M141" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N141" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O141" s="7" t="s">
+      <c r="N141" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O141" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P141" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q141" s="17">
+      <c r="Q141" s="18">
         <v>46155</v>
       </c>
-      <c r="R141" s="18">
+      <c r="R141" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="142" spans="1:18">
-      <c r="A142" s="6" t="s">
+    <row r="142" spans="1:18" hidden="1">
+      <c r="A142" s="7" t="s">
         <v>369</v>
       </c>
       <c r="B142" s="1" t="s">
@@ -11314,29 +11338,29 @@
       <c r="L142" s="2">
         <v>206741</v>
       </c>
-      <c r="M142" s="4" t="s">
+      <c r="M142" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N142" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O142" s="7" t="s">
+      <c r="N142" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O142" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P142" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q142" s="17">
+      <c r="Q142" s="18">
         <v>46155</v>
       </c>
-      <c r="R142" s="18">
+      <c r="R142" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="143" spans="1:18">
-      <c r="A143" s="6" t="s">
+    <row r="143" spans="1:18" hidden="1">
+      <c r="A143" s="7" t="s">
         <v>371</v>
       </c>
       <c r="B143" s="1" t="s">
@@ -11372,29 +11396,29 @@
       <c r="L143" s="2">
         <v>32363</v>
       </c>
-      <c r="M143" s="4" t="s">
+      <c r="M143" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N143" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O143" s="7" t="s">
+      <c r="N143" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O143" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P143" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q143" s="17">
+      <c r="Q143" s="18">
         <v>46155</v>
       </c>
-      <c r="R143" s="18">
+      <c r="R143" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="144" spans="1:18">
-      <c r="A144" s="6" t="s">
+    <row r="144" spans="1:18" hidden="1">
+      <c r="A144" s="7" t="s">
         <v>372</v>
       </c>
       <c r="B144" s="1" t="s">
@@ -11430,29 +11454,29 @@
       <c r="L144" s="2">
         <v>95804</v>
       </c>
-      <c r="M144" s="4" t="s">
+      <c r="M144" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N144" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O144" s="7" t="s">
+      <c r="N144" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O144" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P144" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q144" s="17">
+      <c r="Q144" s="18">
         <v>46155</v>
       </c>
-      <c r="R144" s="18">
+      <c r="R144" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="145" spans="1:18">
-      <c r="A145" s="6" t="s">
+    <row r="145" spans="1:18" hidden="1">
+      <c r="A145" s="7" t="s">
         <v>373</v>
       </c>
       <c r="B145" s="1" t="s">
@@ -11488,29 +11512,29 @@
       <c r="L145" s="2">
         <v>142081</v>
       </c>
-      <c r="M145" s="4" t="s">
+      <c r="M145" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N145" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O145" s="7" t="s">
+      <c r="N145" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O145" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P145" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q145" s="17">
+      <c r="Q145" s="18">
         <v>46155</v>
       </c>
-      <c r="R145" s="18">
+      <c r="R145" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="146" spans="1:18">
-      <c r="A146" s="6" t="s">
+    <row r="146" spans="1:18" hidden="1">
+      <c r="A146" s="7" t="s">
         <v>374</v>
       </c>
       <c r="B146" s="1" t="s">
@@ -11546,29 +11570,29 @@
       <c r="L146" s="2">
         <v>88011</v>
       </c>
-      <c r="M146" s="4" t="s">
+      <c r="M146" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N146" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O146" s="7" t="s">
+      <c r="N146" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O146" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P146" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q146" s="17">
+      <c r="Q146" s="18">
         <v>46155</v>
       </c>
-      <c r="R146" s="18">
+      <c r="R146" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="147" spans="1:18">
-      <c r="A147" s="6" t="s">
+    <row r="147" spans="1:18" hidden="1">
+      <c r="A147" s="7" t="s">
         <v>377</v>
       </c>
       <c r="B147" s="1" t="s">
@@ -11604,29 +11628,29 @@
       <c r="L147" s="2">
         <v>187716</v>
       </c>
-      <c r="M147" s="4" t="s">
+      <c r="M147" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N147" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O147" s="7" t="s">
+      <c r="N147" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O147" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P147" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q147" s="17">
+      <c r="Q147" s="18">
         <v>46155</v>
       </c>
-      <c r="R147" s="18">
+      <c r="R147" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="148" spans="1:18">
-      <c r="A148" s="6" t="s">
+    <row r="148" spans="1:18" hidden="1">
+      <c r="A148" s="7" t="s">
         <v>378</v>
       </c>
       <c r="B148" s="1" t="s">
@@ -11662,29 +11686,29 @@
       <c r="L148" s="2">
         <v>170764</v>
       </c>
-      <c r="M148" s="4" t="s">
+      <c r="M148" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N148" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O148" s="7" t="s">
+      <c r="N148" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O148" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P148" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q148" s="17">
+      <c r="Q148" s="18">
         <v>46155</v>
       </c>
-      <c r="R148" s="18">
+      <c r="R148" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="149" spans="1:18">
-      <c r="A149" s="6" t="s">
+    <row r="149" spans="1:18" hidden="1">
+      <c r="A149" s="7" t="s">
         <v>380</v>
       </c>
       <c r="B149" s="1" t="s">
@@ -11720,29 +11744,29 @@
       <c r="L149" s="2">
         <v>59811</v>
       </c>
-      <c r="M149" s="4" t="s">
+      <c r="M149" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N149" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O149" s="7" t="s">
+      <c r="N149" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O149" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P149" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q149" s="17">
+      <c r="Q149" s="18">
         <v>46155</v>
       </c>
-      <c r="R149" s="18">
+      <c r="R149" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="150" spans="1:18">
-      <c r="A150" s="6" t="s">
+    <row r="150" spans="1:18" hidden="1">
+      <c r="A150" s="7" t="s">
         <v>381</v>
       </c>
       <c r="B150" s="1" t="s">
@@ -11778,29 +11802,29 @@
       <c r="L150" s="2">
         <v>112204</v>
       </c>
-      <c r="M150" s="4" t="s">
+      <c r="M150" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N150" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O150" s="7" t="s">
+      <c r="N150" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O150" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P150" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q150" s="17">
+      <c r="Q150" s="18">
         <v>46155</v>
       </c>
-      <c r="R150" s="18">
+      <c r="R150" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="151" spans="1:18">
-      <c r="A151" s="6" t="s">
+    <row r="151" spans="1:18" hidden="1">
+      <c r="A151" s="7" t="s">
         <v>382</v>
       </c>
       <c r="B151" s="1" t="s">
@@ -11836,29 +11860,29 @@
       <c r="L151" s="2">
         <v>58886</v>
       </c>
-      <c r="M151" s="4" t="s">
+      <c r="M151" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N151" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O151" s="7" t="s">
+      <c r="N151" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O151" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P151" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q151" s="17">
+      <c r="Q151" s="18">
         <v>46155</v>
       </c>
-      <c r="R151" s="18">
+      <c r="R151" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="152" spans="1:18">
-      <c r="A152" s="6" t="s">
+    <row r="152" spans="1:18" hidden="1">
+      <c r="A152" s="7" t="s">
         <v>383</v>
       </c>
       <c r="B152" s="1" t="s">
@@ -11894,29 +11918,29 @@
       <c r="L152" s="2">
         <v>138269</v>
       </c>
-      <c r="M152" s="4" t="s">
+      <c r="M152" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N152" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O152" s="7" t="s">
+      <c r="N152" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O152" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P152" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q152" s="17">
+      <c r="Q152" s="18">
         <v>46155</v>
       </c>
-      <c r="R152" s="18">
+      <c r="R152" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="153" spans="1:18">
-      <c r="A153" s="6" t="s">
+    <row r="153" spans="1:18" hidden="1">
+      <c r="A153" s="7" t="s">
         <v>384</v>
       </c>
       <c r="B153" s="1" t="s">
@@ -11952,29 +11976,29 @@
       <c r="L153" s="2">
         <v>94691</v>
       </c>
-      <c r="M153" s="4" t="s">
+      <c r="M153" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N153" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O153" s="7" t="s">
+      <c r="N153" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O153" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P153" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q153" s="17">
+      <c r="Q153" s="18">
         <v>46155</v>
       </c>
-      <c r="R153" s="18">
+      <c r="R153" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="154" spans="1:18">
-      <c r="A154" s="6" t="s">
+    <row r="154" spans="1:18" hidden="1">
+      <c r="A154" s="7" t="s">
         <v>385</v>
       </c>
       <c r="B154" s="1" t="s">
@@ -12010,29 +12034,29 @@
       <c r="L154" s="2">
         <v>529545</v>
       </c>
-      <c r="M154" s="4" t="s">
+      <c r="M154" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N154" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O154" s="7" t="s">
+      <c r="N154" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O154" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P154" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q154" s="17">
+      <c r="Q154" s="18">
         <v>46155</v>
       </c>
-      <c r="R154" s="18">
+      <c r="R154" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="155" spans="1:18">
-      <c r="A155" s="6" t="s">
+    <row r="155" spans="1:18" hidden="1">
+      <c r="A155" s="7" t="s">
         <v>387</v>
       </c>
       <c r="B155" s="1" t="s">
@@ -12068,29 +12092,29 @@
       <c r="L155" s="2">
         <v>212066</v>
       </c>
-      <c r="M155" s="4" t="s">
+      <c r="M155" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N155" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O155" s="7" t="s">
+      <c r="N155" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O155" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P155" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q155" s="17">
+      <c r="Q155" s="18">
         <v>46155</v>
       </c>
-      <c r="R155" s="18">
+      <c r="R155" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="156" spans="1:18">
-      <c r="A156" s="6" t="s">
+    <row r="156" spans="1:18" hidden="1">
+      <c r="A156" s="7" t="s">
         <v>388</v>
       </c>
       <c r="B156" s="1" t="s">
@@ -12126,29 +12150,29 @@
       <c r="L156" s="2">
         <v>107246</v>
       </c>
-      <c r="M156" s="4" t="s">
+      <c r="M156" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N156" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O156" s="7" t="s">
+      <c r="N156" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O156" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P156" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q156" s="17">
+      <c r="Q156" s="18">
         <v>46155</v>
       </c>
-      <c r="R156" s="18">
+      <c r="R156" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="157" spans="1:18">
-      <c r="A157" s="6" t="s">
+    <row r="157" spans="1:18" hidden="1">
+      <c r="A157" s="7" t="s">
         <v>389</v>
       </c>
       <c r="B157" s="1" t="s">
@@ -12184,29 +12208,29 @@
       <c r="L157" s="2">
         <v>108585</v>
       </c>
-      <c r="M157" s="4" t="s">
+      <c r="M157" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N157" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O157" s="7" t="s">
+      <c r="N157" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O157" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P157" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q157" s="17">
+      <c r="Q157" s="18">
         <v>46155</v>
       </c>
-      <c r="R157" s="18">
+      <c r="R157" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="158" spans="1:18">
-      <c r="A158" s="6" t="s">
+    <row r="158" spans="1:18" hidden="1">
+      <c r="A158" s="7" t="s">
         <v>390</v>
       </c>
       <c r="B158" s="1" t="s">
@@ -12242,29 +12266,29 @@
       <c r="L158" s="2">
         <v>70855</v>
       </c>
-      <c r="M158" s="4" t="s">
+      <c r="M158" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N158" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O158" s="7" t="s">
+      <c r="N158" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O158" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P158" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q158" s="17">
+      <c r="Q158" s="18">
         <v>46155</v>
       </c>
-      <c r="R158" s="18">
+      <c r="R158" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="159" spans="1:18">
-      <c r="A159" s="6" t="s">
+    <row r="159" spans="1:18" hidden="1">
+      <c r="A159" s="7" t="s">
         <v>395</v>
       </c>
       <c r="B159" s="1" t="s">
@@ -12300,29 +12324,29 @@
       <c r="L159" s="2">
         <v>217211</v>
       </c>
-      <c r="M159" s="4" t="s">
+      <c r="M159" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N159" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O159" s="7" t="s">
+      <c r="N159" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O159" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P159" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q159" s="17">
+      <c r="Q159" s="18">
         <v>46155</v>
       </c>
-      <c r="R159" s="18">
+      <c r="R159" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="160" spans="1:18">
-      <c r="A160" s="6" t="s">
+    <row r="160" spans="1:18" hidden="1">
+      <c r="A160" s="7" t="s">
         <v>397</v>
       </c>
       <c r="B160" s="1" t="s">
@@ -12358,29 +12382,29 @@
       <c r="L160" s="2">
         <v>205370</v>
       </c>
-      <c r="M160" s="4" t="s">
+      <c r="M160" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N160" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O160" s="7" t="s">
+      <c r="N160" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O160" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P160" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q160" s="17">
+      <c r="Q160" s="18">
         <v>46155</v>
       </c>
-      <c r="R160" s="18">
+      <c r="R160" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="161" spans="1:18">
-      <c r="A161" s="6" t="s">
+    <row r="161" spans="1:18" hidden="1">
+      <c r="A161" s="7" t="s">
         <v>398</v>
       </c>
       <c r="B161" s="1" t="s">
@@ -12416,29 +12440,29 @@
       <c r="L161" s="2">
         <v>263205</v>
       </c>
-      <c r="M161" s="4" t="s">
+      <c r="M161" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N161" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O161" s="7" t="s">
+      <c r="N161" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O161" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P161" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q161" s="17">
+      <c r="Q161" s="18">
         <v>46155</v>
       </c>
-      <c r="R161" s="18">
+      <c r="R161" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="162" spans="1:18">
-      <c r="A162" s="6" t="s">
+    <row r="162" spans="1:18" hidden="1">
+      <c r="A162" s="7" t="s">
         <v>399</v>
       </c>
       <c r="B162" s="1" t="s">
@@ -12474,29 +12498,29 @@
       <c r="L162" s="2">
         <v>195655</v>
       </c>
-      <c r="M162" s="4" t="s">
+      <c r="M162" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N162" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O162" s="7" t="s">
+      <c r="N162" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O162" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P162" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q162" s="17">
+      <c r="Q162" s="18">
         <v>46155</v>
       </c>
-      <c r="R162" s="18">
+      <c r="R162" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="163" spans="1:18">
-      <c r="A163" s="6" t="s">
+    <row r="163" spans="1:18" hidden="1">
+      <c r="A163" s="7" t="s">
         <v>403</v>
       </c>
       <c r="B163" s="1" t="s">
@@ -12532,29 +12556,29 @@
       <c r="L163" s="2">
         <v>259920</v>
       </c>
-      <c r="M163" s="4" t="s">
+      <c r="M163" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N163" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O163" s="7" t="s">
+      <c r="N163" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O163" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P163" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q163" s="17">
+      <c r="Q163" s="18">
         <v>46155</v>
       </c>
-      <c r="R163" s="18">
+      <c r="R163" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="164" spans="1:18">
-      <c r="A164" s="6" t="s">
+    <row r="164" spans="1:18" hidden="1">
+      <c r="A164" s="7" t="s">
         <v>405</v>
       </c>
       <c r="B164" s="1" t="s">
@@ -12590,29 +12614,29 @@
       <c r="L164" s="2">
         <v>234360</v>
       </c>
-      <c r="M164" s="4" t="s">
+      <c r="M164" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N164" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O164" s="7" t="s">
+      <c r="N164" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O164" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P164" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q164" s="17">
+      <c r="Q164" s="18">
         <v>46155</v>
       </c>
-      <c r="R164" s="18">
+      <c r="R164" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="165" spans="1:18">
-      <c r="A165" s="6" t="s">
+    <row r="165" spans="1:18" hidden="1">
+      <c r="A165" s="7" t="s">
         <v>407</v>
       </c>
       <c r="B165" s="1" t="s">
@@ -12648,29 +12672,29 @@
       <c r="L165" s="2">
         <v>66504</v>
       </c>
-      <c r="M165" s="4" t="s">
+      <c r="M165" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N165" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O165" s="7" t="s">
+      <c r="N165" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O165" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P165" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q165" s="17">
+      <c r="Q165" s="18">
         <v>46155</v>
       </c>
-      <c r="R165" s="18">
+      <c r="R165" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="166" spans="1:18">
-      <c r="A166" s="6" t="s">
+    <row r="166" spans="1:18" hidden="1">
+      <c r="A166" s="7" t="s">
         <v>410</v>
       </c>
       <c r="B166" s="1" t="s">
@@ -12706,29 +12730,29 @@
       <c r="L166" s="2">
         <v>135899</v>
       </c>
-      <c r="M166" s="4" t="s">
+      <c r="M166" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N166" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O166" s="7" t="s">
+      <c r="N166" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O166" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P166" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q166" s="17">
+      <c r="Q166" s="18">
         <v>46155</v>
       </c>
-      <c r="R166" s="18">
+      <c r="R166" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="167" spans="1:18">
-      <c r="A167" s="6" t="s">
+    <row r="167" spans="1:18" hidden="1">
+      <c r="A167" s="7" t="s">
         <v>412</v>
       </c>
       <c r="B167" s="1" t="s">
@@ -12764,29 +12788,29 @@
       <c r="L167" s="2">
         <v>166499</v>
       </c>
-      <c r="M167" s="4" t="s">
+      <c r="M167" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N167" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O167" s="7" t="s">
+      <c r="N167" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O167" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P167" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q167" s="17">
+      <c r="Q167" s="18">
         <v>46155</v>
       </c>
-      <c r="R167" s="18">
+      <c r="R167" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="168" spans="1:18">
-      <c r="A168" s="6" t="s">
+    <row r="168" spans="1:18" hidden="1">
+      <c r="A168" s="7" t="s">
         <v>413</v>
       </c>
       <c r="B168" s="1" t="s">
@@ -12822,29 +12846,29 @@
       <c r="L168" s="2">
         <v>549915</v>
       </c>
-      <c r="M168" s="4" t="s">
+      <c r="M168" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N168" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O168" s="7" t="s">
+      <c r="N168" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O168" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P168" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q168" s="17">
+      <c r="Q168" s="18">
         <v>46155</v>
       </c>
-      <c r="R168" s="18">
+      <c r="R168" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="169" spans="1:18">
-      <c r="A169" s="6" t="s">
+    <row r="169" spans="1:18" hidden="1">
+      <c r="A169" s="7" t="s">
         <v>415</v>
       </c>
       <c r="B169" s="1" t="s">
@@ -12880,29 +12904,29 @@
       <c r="L169" s="2">
         <v>111777</v>
       </c>
-      <c r="M169" s="4" t="s">
+      <c r="M169" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N169" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O169" s="7" t="s">
+      <c r="N169" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O169" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P169" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q169" s="17">
+      <c r="Q169" s="18">
         <v>46155</v>
       </c>
-      <c r="R169" s="18">
+      <c r="R169" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="170" spans="1:18">
-      <c r="A170" s="6" t="s">
+    <row r="170" spans="1:18" hidden="1">
+      <c r="A170" s="7" t="s">
         <v>417</v>
       </c>
       <c r="B170" s="1" t="s">
@@ -12938,29 +12962,29 @@
       <c r="L170" s="2">
         <v>32307</v>
       </c>
-      <c r="M170" s="4" t="s">
+      <c r="M170" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N170" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O170" s="7" t="s">
+      <c r="N170" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O170" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P170" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q170" s="17">
+      <c r="Q170" s="18">
         <v>46155</v>
       </c>
-      <c r="R170" s="18">
+      <c r="R170" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="171" spans="1:18">
-      <c r="A171" s="6" t="s">
+    <row r="171" spans="1:18" hidden="1">
+      <c r="A171" s="7" t="s">
         <v>418</v>
       </c>
       <c r="B171" s="1" t="s">
@@ -12996,29 +13020,29 @@
       <c r="L171" s="2">
         <v>216032</v>
       </c>
-      <c r="M171" s="4" t="s">
+      <c r="M171" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N171" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O171" s="7" t="s">
+      <c r="N171" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O171" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P171" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q171" s="17">
+      <c r="Q171" s="18">
         <v>46155</v>
       </c>
-      <c r="R171" s="18">
+      <c r="R171" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="172" spans="1:18">
-      <c r="A172" s="6" t="s">
+    <row r="172" spans="1:18" hidden="1">
+      <c r="A172" s="7" t="s">
         <v>420</v>
       </c>
       <c r="B172" s="1" t="s">
@@ -13054,29 +13078,29 @@
       <c r="L172" s="2">
         <v>1048670</v>
       </c>
-      <c r="M172" s="4" t="s">
+      <c r="M172" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N172" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O172" s="7" t="s">
+      <c r="N172" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O172" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P172" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q172" s="17">
+      <c r="Q172" s="18">
         <v>46155</v>
       </c>
-      <c r="R172" s="18">
+      <c r="R172" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="173" spans="1:18">
-      <c r="A173" s="6" t="s">
+    <row r="173" spans="1:18" hidden="1">
+      <c r="A173" s="7" t="s">
         <v>424</v>
       </c>
       <c r="B173" s="1" t="s">
@@ -13112,29 +13136,29 @@
       <c r="L173" s="2">
         <v>10458712</v>
       </c>
-      <c r="M173" s="4" t="s">
+      <c r="M173" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N173" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O173" s="7" t="s">
+      <c r="N173" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O173" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P173" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q173" s="17">
+      <c r="Q173" s="18">
         <v>46155</v>
       </c>
-      <c r="R173" s="18">
+      <c r="R173" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="174" spans="1:18">
-      <c r="A174" s="6" t="s">
+    <row r="174" spans="1:18" hidden="1">
+      <c r="A174" s="7" t="s">
         <v>426</v>
       </c>
       <c r="B174" s="1" t="s">
@@ -13170,29 +13194,29 @@
       <c r="L174" s="2">
         <v>66533</v>
       </c>
-      <c r="M174" s="4" t="s">
+      <c r="M174" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N174" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O174" s="7" t="s">
+      <c r="N174" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O174" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P174" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q174" s="17">
+      <c r="Q174" s="18">
         <v>46155</v>
       </c>
-      <c r="R174" s="18">
+      <c r="R174" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="175" spans="1:18">
-      <c r="A175" s="5" t="s">
+    <row r="175" spans="1:18" hidden="1">
+      <c r="A175" s="6" t="s">
         <v>428</v>
       </c>
       <c r="B175" s="1" t="s">
@@ -13228,29 +13252,29 @@
       <c r="L175" s="2">
         <v>15082353</v>
       </c>
-      <c r="M175" s="4" t="s">
+      <c r="M175" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="N175" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O175" s="7" t="s">
+      <c r="N175" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O175" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P175" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q175" s="17">
+      <c r="Q175" s="18">
         <v>46155</v>
       </c>
-      <c r="R175" s="18">
+      <c r="R175" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="176" spans="1:18">
-      <c r="A176" s="6" t="s">
+    <row r="176" spans="1:18" hidden="1">
+      <c r="A176" s="7" t="s">
         <v>430</v>
       </c>
       <c r="B176" s="1" t="s">
@@ -13286,29 +13310,29 @@
       <c r="L176" s="2">
         <v>18103582</v>
       </c>
-      <c r="M176" s="4" t="s">
+      <c r="M176" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="N176" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O176" s="7" t="s">
+      <c r="N176" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O176" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P176" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q176" s="17">
+      <c r="Q176" s="18">
         <v>46155</v>
       </c>
-      <c r="R176" s="18">
+      <c r="R176" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="177" spans="1:18">
-      <c r="A177" s="6" t="s">
+    <row r="177" spans="1:18" hidden="1">
+      <c r="A177" s="7" t="s">
         <v>440</v>
       </c>
       <c r="B177" s="1" t="s">
@@ -13344,29 +13368,29 @@
       <c r="L177" s="2">
         <v>30787</v>
       </c>
-      <c r="M177" s="4" t="s">
+      <c r="M177" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N177" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O177" s="7" t="s">
+      <c r="N177" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O177" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P177" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q177" s="17">
+      <c r="Q177" s="18">
         <v>46155</v>
       </c>
-      <c r="R177" s="18">
+      <c r="R177" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
-    <row r="178" spans="1:18">
-      <c r="A178" s="6" t="s">
+    <row r="178" spans="1:18" hidden="1">
+      <c r="A178" s="7" t="s">
         <v>443</v>
       </c>
       <c r="B178" s="1" t="s">
@@ -13402,29 +13426,29 @@
       <c r="L178" s="2">
         <v>9200</v>
       </c>
-      <c r="M178" s="4" t="s">
+      <c r="M178" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N178" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O178" s="7" t="s">
+      <c r="N178" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O178" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P178" s="1" t="str">
         <f t="shared" si="2"/>
         <v>13/05/2026</v>
       </c>
-      <c r="Q178" s="17">
+      <c r="Q178" s="18">
         <v>46155</v>
       </c>
-      <c r="R178" s="18">
+      <c r="R178" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-94</v>
       </c>
     </row>
     <row r="179" spans="1:18">
-      <c r="A179" s="6" t="s">
+      <c r="A179" s="7" t="s">
         <v>281</v>
       </c>
       <c r="B179" s="1" t="s">
@@ -13439,7 +13463,7 @@
       <c r="E179" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F179" s="1">
+      <c r="F179" s="2">
         <v>14</v>
       </c>
       <c r="G179" s="1" t="s">
@@ -13460,27 +13484,26 @@
       <c r="L179" s="2">
         <v>6958000</v>
       </c>
-      <c r="M179" s="4" t="s">
+      <c r="M179" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="N179" s="7" t="s">
+      <c r="N179" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O179" s="7"/>
-      <c r="P179" s="1" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q179" s="17" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="R179" s="18" t="e">
-        <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="180" spans="1:18">
-      <c r="A180" s="6" t="s">
+      <c r="O179" s="8"/>
+      <c r="P179" s="22">
+        <v>46163</v>
+      </c>
+      <c r="Q179" s="18">
+        <v>46163</v>
+      </c>
+      <c r="R179" s="19">
+        <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
+        <v>-86</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" hidden="1">
+      <c r="A180" s="7" t="s">
         <v>409</v>
       </c>
       <c r="B180" s="1" t="s">
@@ -13517,26 +13540,26 @@
         <v>6843373</v>
       </c>
       <c r="M180" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="N180" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="N180" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O180" s="7"/>
+      <c r="O180" s="8"/>
       <c r="P180" s="1" t="str">
         <f t="shared" si="2"/>
         <v>27/06/2026</v>
       </c>
-      <c r="Q180" s="17">
+      <c r="Q180" s="18">
         <v>46200</v>
       </c>
-      <c r="R180" s="18">
+      <c r="R180" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-49</v>
       </c>
     </row>
-    <row r="181" spans="1:18">
-      <c r="A181" s="6" t="s">
+    <row r="181" spans="1:18" hidden="1">
+      <c r="A181" s="7" t="s">
         <v>263</v>
       </c>
       <c r="B181" s="1" t="s">
@@ -13572,29 +13595,29 @@
       <c r="L181" s="2">
         <v>49747408</v>
       </c>
-      <c r="M181" s="4" t="s">
+      <c r="M181" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="N181" s="7" t="s">
+      <c r="N181" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="O181" s="7" t="s">
-        <v>510</v>
+      <c r="O181" s="8" t="s">
+        <v>509</v>
       </c>
       <c r="P181" s="1" t="str">
         <f t="shared" si="2"/>
         <v>04/06/2026</v>
       </c>
-      <c r="Q181" s="17">
+      <c r="Q181" s="18">
         <v>46177</v>
       </c>
-      <c r="R181" s="18">
+      <c r="R181" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-72</v>
       </c>
     </row>
-    <row r="182" spans="1:18">
-      <c r="A182" s="6" t="s">
+    <row r="182" spans="1:18" hidden="1">
+      <c r="A182" s="7" t="s">
         <v>93</v>
       </c>
       <c r="B182" s="1" t="s">
@@ -13631,26 +13654,26 @@
         <v>6594671</v>
       </c>
       <c r="M182" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="N182" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="N182" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O182" s="7"/>
+      <c r="O182" s="8"/>
       <c r="P182" s="1" t="str">
         <f t="shared" si="2"/>
         <v>11/8/2026</v>
       </c>
-      <c r="Q182" s="17">
+      <c r="Q182" s="18">
         <v>46245</v>
       </c>
-      <c r="R182" s="18">
+      <c r="R182" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-4</v>
       </c>
     </row>
-    <row r="183" spans="1:18">
-      <c r="A183" s="6" t="s">
+    <row r="183" spans="1:18" hidden="1">
+      <c r="A183" s="7" t="s">
         <v>203</v>
       </c>
       <c r="B183" s="1" t="s">
@@ -13687,26 +13710,26 @@
         <v>5926415</v>
       </c>
       <c r="M183" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="N183" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="N183" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O183" s="7"/>
+      <c r="O183" s="8"/>
       <c r="P183" s="1" t="str">
         <f t="shared" si="2"/>
         <v>23/06/2026</v>
       </c>
-      <c r="Q183" s="17">
+      <c r="Q183" s="18">
         <v>46196</v>
       </c>
-      <c r="R183" s="18">
+      <c r="R183" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-53</v>
       </c>
     </row>
     <row r="184" spans="1:18">
-      <c r="A184" s="6" t="s">
+      <c r="A184" s="7" t="s">
         <v>269</v>
       </c>
       <c r="B184" s="1" t="s">
@@ -13721,7 +13744,7 @@
       <c r="E184" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F184" s="1">
+      <c r="F184" s="2">
         <v>85</v>
       </c>
       <c r="G184" s="1" t="s">
@@ -13742,27 +13765,27 @@
       <c r="L184" s="2">
         <v>5678688</v>
       </c>
-      <c r="M184" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N184" s="7" t="s">
+      <c r="M184" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="N184" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O184" s="7"/>
-      <c r="P184" s="1" t="e">
+      <c r="O184" s="8"/>
+      <c r="P184" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q184" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R184" s="18" t="e">
-        <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="185" spans="1:18">
-      <c r="A185" s="6" t="s">
+        <v>23/5/2025</v>
+      </c>
+      <c r="Q184" s="23">
+        <v>46165</v>
+      </c>
+      <c r="R184" s="19">
+        <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
+        <v>-84</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" hidden="1">
+      <c r="A185" s="7" t="s">
         <v>252</v>
       </c>
       <c r="B185" s="1" t="s">
@@ -13799,26 +13822,26 @@
         <v>4537774</v>
       </c>
       <c r="M185" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="N185" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="N185" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O185" s="7"/>
+      <c r="O185" s="8"/>
       <c r="P185" s="1" t="str">
         <f t="shared" si="2"/>
         <v>23/7/2026</v>
       </c>
-      <c r="Q185" s="17">
+      <c r="Q185" s="18">
         <v>46226</v>
       </c>
-      <c r="R185" s="18">
+      <c r="R185" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-23</v>
       </c>
     </row>
-    <row r="186" spans="1:18">
-      <c r="A186" s="6" t="s">
+    <row r="186" spans="1:18" hidden="1">
+      <c r="A186" s="7" t="s">
         <v>53</v>
       </c>
       <c r="B186" s="1" t="s">
@@ -13854,27 +13877,27 @@
       <c r="L186" s="2">
         <v>4305041</v>
       </c>
-      <c r="M186" s="4" t="s">
+      <c r="M186" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="N186" s="7" t="s">
+      <c r="N186" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O186" s="7"/>
+      <c r="O186" s="8"/>
       <c r="P186" s="1" t="str">
         <f t="shared" si="2"/>
         <v>05/11/2024</v>
       </c>
-      <c r="Q186" s="17">
+      <c r="Q186" s="18">
         <v>45601</v>
       </c>
-      <c r="R186" s="18">
+      <c r="R186" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-648</v>
       </c>
     </row>
-    <row r="187" spans="1:18">
-      <c r="A187" s="6" t="s">
+    <row r="187" spans="1:18" hidden="1">
+      <c r="A187" s="7" t="s">
         <v>56</v>
       </c>
       <c r="B187" s="1" t="s">
@@ -13910,27 +13933,27 @@
       <c r="L187" s="2">
         <v>4305041</v>
       </c>
-      <c r="M187" s="4" t="s">
+      <c r="M187" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="N187" s="7" t="s">
+      <c r="N187" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O187" s="7"/>
+      <c r="O187" s="8"/>
       <c r="P187" s="1" t="str">
         <f t="shared" si="2"/>
         <v>05/11/2024</v>
       </c>
-      <c r="Q187" s="17">
+      <c r="Q187" s="18">
         <v>45601</v>
       </c>
-      <c r="R187" s="18">
+      <c r="R187" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-648</v>
       </c>
     </row>
-    <row r="188" spans="1:18">
-      <c r="A188" s="6" t="s">
+    <row r="188" spans="1:18" hidden="1">
+      <c r="A188" s="7" t="s">
         <v>125</v>
       </c>
       <c r="B188" s="1" t="s">
@@ -13967,26 +13990,26 @@
         <v>3657181</v>
       </c>
       <c r="M188" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="N188" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="N188" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O188" s="7"/>
+      <c r="O188" s="8"/>
       <c r="P188" s="1" t="str">
         <f t="shared" si="2"/>
         <v>19/05/2026</v>
       </c>
-      <c r="Q188" s="17">
+      <c r="Q188" s="18">
         <v>46161</v>
       </c>
-      <c r="R188" s="18">
+      <c r="R188" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-88</v>
       </c>
     </row>
-    <row r="189" spans="1:18">
-      <c r="A189" s="6" t="s">
+    <row r="189" spans="1:18" hidden="1">
+      <c r="A189" s="7" t="s">
         <v>89</v>
       </c>
       <c r="B189" s="1" t="s">
@@ -14023,26 +14046,26 @@
         <v>3297166</v>
       </c>
       <c r="M189" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="N189" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="N189" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O189" s="7"/>
+      <c r="O189" s="8"/>
       <c r="P189" s="1" t="str">
         <f t="shared" si="2"/>
         <v>11/8/2026</v>
       </c>
-      <c r="Q189" s="17">
+      <c r="Q189" s="18">
         <v>46245</v>
       </c>
-      <c r="R189" s="18">
+      <c r="R189" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-4</v>
       </c>
     </row>
-    <row r="190" spans="1:18">
-      <c r="A190" s="6" t="s">
+    <row r="190" spans="1:18" hidden="1">
+      <c r="A190" s="7" t="s">
         <v>173</v>
       </c>
       <c r="B190" s="1" t="s">
@@ -14079,26 +14102,26 @@
         <v>2303955</v>
       </c>
       <c r="M190" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="N190" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="N190" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O190" s="7"/>
+      <c r="O190" s="8"/>
       <c r="P190" s="1" t="str">
         <f t="shared" si="2"/>
         <v>5/8/2026</v>
       </c>
-      <c r="Q190" s="17">
+      <c r="Q190" s="18">
         <v>46239</v>
       </c>
-      <c r="R190" s="18">
+      <c r="R190" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-10</v>
       </c>
     </row>
-    <row r="191" spans="1:18">
-      <c r="A191" s="6" t="s">
+    <row r="191" spans="1:18" hidden="1">
+      <c r="A191" s="7" t="s">
         <v>261</v>
       </c>
       <c r="B191" s="1" t="s">
@@ -14135,26 +14158,26 @@
         <v>2196697</v>
       </c>
       <c r="M191" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="N191" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="N191" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O191" s="7"/>
+      <c r="O191" s="8"/>
       <c r="P191" s="1" t="str">
         <f t="shared" si="2"/>
         <v>12/5/2026</v>
       </c>
-      <c r="Q191" s="17">
+      <c r="Q191" s="18">
         <v>46154</v>
       </c>
-      <c r="R191" s="18">
+      <c r="R191" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-95</v>
       </c>
     </row>
-    <row r="192" spans="1:18">
-      <c r="A192" s="6" t="s">
+    <row r="192" spans="1:18" hidden="1">
+      <c r="A192" s="7" t="s">
         <v>235</v>
       </c>
       <c r="B192" s="1" t="s">
@@ -14191,26 +14214,26 @@
         <v>2156809</v>
       </c>
       <c r="M192" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="N192" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="N192" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O192" s="7"/>
+      <c r="O192" s="8"/>
       <c r="P192" s="1" t="str">
         <f t="shared" si="2"/>
         <v>02/07/2026</v>
       </c>
-      <c r="Q192" s="17">
+      <c r="Q192" s="18">
         <v>46205</v>
       </c>
-      <c r="R192" s="18">
+      <c r="R192" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-44</v>
       </c>
     </row>
-    <row r="193" spans="1:18">
-      <c r="A193" s="6" t="s">
+    <row r="193" spans="1:18" hidden="1">
+      <c r="A193" s="7" t="s">
         <v>279</v>
       </c>
       <c r="B193" s="1" t="s">
@@ -14247,26 +14270,26 @@
         <v>2100000</v>
       </c>
       <c r="M193" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="N193" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="N193" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O193" s="7"/>
+      <c r="O193" s="8"/>
       <c r="P193" s="1" t="str">
         <f t="shared" si="2"/>
         <v>16/07/2026</v>
       </c>
-      <c r="Q193" s="17">
+      <c r="Q193" s="18">
         <v>46219</v>
       </c>
-      <c r="R193" s="18">
+      <c r="R193" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-30</v>
       </c>
     </row>
-    <row r="194" spans="1:18">
-      <c r="A194" s="6" t="s">
+    <row r="194" spans="1:18" hidden="1">
+      <c r="A194" s="7" t="s">
         <v>111</v>
       </c>
       <c r="B194" s="1" t="s">
@@ -14303,26 +14326,26 @@
         <v>2039567</v>
       </c>
       <c r="M194" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="N194" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="N194" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O194" s="7"/>
+      <c r="O194" s="8"/>
       <c r="P194" s="1" t="str">
         <f t="shared" ref="P194:P218" si="3">LEFT(M194,FIND("_",M194)-1)</f>
         <v>20/7/2026</v>
       </c>
-      <c r="Q194" s="17">
+      <c r="Q194" s="18">
         <v>46223</v>
       </c>
-      <c r="R194" s="18">
+      <c r="R194" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-26</v>
       </c>
     </row>
-    <row r="195" spans="1:18">
-      <c r="A195" s="6" t="s">
+    <row r="195" spans="1:18" hidden="1">
+      <c r="A195" s="7" t="s">
         <v>164</v>
       </c>
       <c r="B195" s="1" t="s">
@@ -14359,26 +14382,26 @@
         <v>1935689</v>
       </c>
       <c r="M195" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="N195" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="N195" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O195" s="7"/>
+      <c r="O195" s="8"/>
       <c r="P195" s="1" t="str">
         <f t="shared" si="3"/>
         <v>31/7/2026</v>
       </c>
-      <c r="Q195" s="17">
+      <c r="Q195" s="18">
         <v>46234</v>
       </c>
-      <c r="R195" s="18">
+      <c r="R195" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-15</v>
       </c>
     </row>
-    <row r="196" spans="1:18">
-      <c r="A196" s="6" t="s">
+    <row r="196" spans="1:18" hidden="1">
+      <c r="A196" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B196" s="1" t="s">
@@ -14415,26 +14438,26 @@
         <v>1838936</v>
       </c>
       <c r="M196" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="N196" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="N196" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O196" s="7"/>
+      <c r="O196" s="8"/>
       <c r="P196" s="1" t="str">
         <f t="shared" si="3"/>
         <v>04/06/2026</v>
       </c>
-      <c r="Q196" s="17">
+      <c r="Q196" s="18">
         <v>46177</v>
       </c>
-      <c r="R196" s="18">
+      <c r="R196" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-72</v>
       </c>
     </row>
-    <row r="197" spans="1:18">
-      <c r="A197" s="6" t="s">
+    <row r="197" spans="1:18" hidden="1">
+      <c r="A197" s="7" t="s">
         <v>432</v>
       </c>
       <c r="B197" s="1" t="s">
@@ -14471,26 +14494,26 @@
         <v>1286039</v>
       </c>
       <c r="M197" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="N197" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="N197" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O197" s="7"/>
+      <c r="O197" s="8"/>
       <c r="P197" s="1" t="str">
         <f t="shared" si="3"/>
         <v>4/8/2026</v>
       </c>
-      <c r="Q197" s="17">
+      <c r="Q197" s="18">
         <v>46238</v>
       </c>
-      <c r="R197" s="18">
+      <c r="R197" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-11</v>
       </c>
     </row>
-    <row r="198" spans="1:18">
-      <c r="A198" s="6" t="s">
+    <row r="198" spans="1:18" hidden="1">
+      <c r="A198" s="7" t="s">
         <v>392</v>
       </c>
       <c r="B198" s="1" t="s">
@@ -14527,26 +14550,26 @@
         <v>1262602</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="N198" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="N198" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O198" s="7"/>
+      <c r="O198" s="8"/>
       <c r="P198" s="1" t="str">
         <f t="shared" si="3"/>
         <v>29/7/2026</v>
       </c>
-      <c r="Q198" s="17">
+      <c r="Q198" s="18">
         <v>46232</v>
       </c>
-      <c r="R198" s="18">
+      <c r="R198" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-17</v>
       </c>
     </row>
-    <row r="199" spans="1:18">
-      <c r="A199" s="6" t="s">
+    <row r="199" spans="1:18" hidden="1">
+      <c r="A199" s="7" t="s">
         <v>271</v>
       </c>
       <c r="B199" s="1" t="s">
@@ -14583,26 +14606,26 @@
         <v>1258950</v>
       </c>
       <c r="M199" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="N199" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="N199" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O199" s="7"/>
+      <c r="O199" s="8"/>
       <c r="P199" s="1" t="str">
         <f t="shared" si="3"/>
         <v>20/07/2026</v>
       </c>
-      <c r="Q199" s="17">
+      <c r="Q199" s="18">
         <v>46223</v>
       </c>
-      <c r="R199" s="18">
+      <c r="R199" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-26</v>
       </c>
     </row>
-    <row r="200" spans="1:18">
-      <c r="A200" s="6" t="s">
+    <row r="200" spans="1:18" hidden="1">
+      <c r="A200" s="7" t="s">
         <v>95</v>
       </c>
       <c r="B200" s="1" t="s">
@@ -14639,26 +14662,26 @@
         <v>1257336</v>
       </c>
       <c r="M200" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="N200" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="N200" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O200" s="7"/>
+      <c r="O200" s="8"/>
       <c r="P200" s="1" t="str">
         <f t="shared" si="3"/>
         <v>6/7/2026</v>
       </c>
-      <c r="Q200" s="17">
+      <c r="Q200" s="18">
         <v>46209</v>
       </c>
-      <c r="R200" s="18">
+      <c r="R200" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-40</v>
       </c>
     </row>
-    <row r="201" spans="1:18">
-      <c r="A201" s="6" t="s">
+    <row r="201" spans="1:18" hidden="1">
+      <c r="A201" s="7" t="s">
         <v>239</v>
       </c>
       <c r="B201" s="1" t="s">
@@ -14695,26 +14718,26 @@
         <v>1159456</v>
       </c>
       <c r="M201" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="N201" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="N201" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O201" s="7"/>
+      <c r="O201" s="8"/>
       <c r="P201" s="1" t="str">
         <f t="shared" si="3"/>
         <v>02/07/2026</v>
       </c>
-      <c r="Q201" s="17">
+      <c r="Q201" s="18">
         <v>46205</v>
       </c>
-      <c r="R201" s="18">
+      <c r="R201" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-44</v>
       </c>
     </row>
-    <row r="202" spans="1:18">
-      <c r="A202" s="6" t="s">
+    <row r="202" spans="1:18" hidden="1">
+      <c r="A202" s="7" t="s">
         <v>250</v>
       </c>
       <c r="B202" s="1" t="s">
@@ -14751,26 +14774,26 @@
         <v>1037894</v>
       </c>
       <c r="M202" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="N202" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="N202" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O202" s="7"/>
+      <c r="O202" s="8"/>
       <c r="P202" s="1" t="str">
         <f t="shared" si="3"/>
         <v>27/5/2026</v>
       </c>
-      <c r="Q202" s="17">
+      <c r="Q202" s="18">
         <v>46169</v>
       </c>
-      <c r="R202" s="18">
+      <c r="R202" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-80</v>
       </c>
     </row>
-    <row r="203" spans="1:18">
-      <c r="A203" s="6" t="s">
+    <row r="203" spans="1:18" hidden="1">
+      <c r="A203" s="7" t="s">
         <v>170</v>
       </c>
       <c r="B203" s="1" t="s">
@@ -14807,26 +14830,26 @@
         <v>698145</v>
       </c>
       <c r="M203" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="N203" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="N203" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O203" s="7"/>
+      <c r="O203" s="8"/>
       <c r="P203" s="1" t="str">
         <f t="shared" si="3"/>
         <v>11/8/2026</v>
       </c>
-      <c r="Q203" s="17">
+      <c r="Q203" s="18">
         <v>46245</v>
       </c>
-      <c r="R203" s="18">
+      <c r="R203" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-4</v>
       </c>
     </row>
-    <row r="204" spans="1:18">
-      <c r="A204" s="6" t="s">
+    <row r="204" spans="1:18" hidden="1">
+      <c r="A204" s="7" t="s">
         <v>82</v>
       </c>
       <c r="B204" s="1" t="s">
@@ -14863,26 +14886,26 @@
         <v>530914</v>
       </c>
       <c r="M204" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="N204" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="N204" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O204" s="7"/>
+      <c r="O204" s="8"/>
       <c r="P204" s="1" t="str">
         <f t="shared" si="3"/>
         <v>5/8/2026</v>
       </c>
-      <c r="Q204" s="17">
+      <c r="Q204" s="18">
         <v>46239</v>
       </c>
-      <c r="R204" s="18">
+      <c r="R204" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-10</v>
       </c>
     </row>
-    <row r="205" spans="1:18">
-      <c r="A205" s="6" t="s">
+    <row r="205" spans="1:18" hidden="1">
+      <c r="A205" s="7" t="s">
         <v>297</v>
       </c>
       <c r="B205" s="1" t="s">
@@ -14919,26 +14942,26 @@
         <v>515777</v>
       </c>
       <c r="M205" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="N205" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="N205" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O205" s="7"/>
+      <c r="O205" s="8"/>
       <c r="P205" s="1" t="str">
         <f t="shared" si="3"/>
         <v>6/8/2026</v>
       </c>
-      <c r="Q205" s="17">
+      <c r="Q205" s="18">
         <v>46240</v>
       </c>
-      <c r="R205" s="18">
+      <c r="R205" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-9</v>
       </c>
     </row>
-    <row r="206" spans="1:18">
-      <c r="A206" s="6" t="s">
+    <row r="206" spans="1:18" hidden="1">
+      <c r="A206" s="7" t="s">
         <v>199</v>
       </c>
       <c r="B206" s="1" t="s">
@@ -14975,26 +14998,26 @@
         <v>479990</v>
       </c>
       <c r="M206" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="N206" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="N206" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O206" s="7"/>
+      <c r="O206" s="8"/>
       <c r="P206" s="1" t="str">
         <f t="shared" si="3"/>
         <v>7/8/2026</v>
       </c>
-      <c r="Q206" s="17">
+      <c r="Q206" s="18">
         <v>46241</v>
       </c>
-      <c r="R206" s="18">
+      <c r="R206" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-8</v>
       </c>
     </row>
-    <row r="207" spans="1:18">
-      <c r="A207" s="6" t="s">
+    <row r="207" spans="1:18" hidden="1">
+      <c r="A207" s="7" t="s">
         <v>172</v>
       </c>
       <c r="B207" s="1" t="s">
@@ -15031,26 +15054,26 @@
         <v>349052</v>
       </c>
       <c r="M207" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="N207" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="N207" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O207" s="7"/>
+      <c r="O207" s="8"/>
       <c r="P207" s="1" t="str">
         <f t="shared" si="3"/>
         <v>13/8/2026</v>
       </c>
-      <c r="Q207" s="17">
+      <c r="Q207" s="18">
         <v>46247</v>
       </c>
-      <c r="R207" s="18">
+      <c r="R207" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-2</v>
       </c>
     </row>
-    <row r="208" spans="1:18">
-      <c r="A208" s="6" t="s">
+    <row r="208" spans="1:18" hidden="1">
+      <c r="A208" s="7" t="s">
         <v>375</v>
       </c>
       <c r="B208" s="1" t="s">
@@ -15087,26 +15110,26 @@
         <v>117344</v>
       </c>
       <c r="M208" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="N208" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="N208" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O208" s="7"/>
+      <c r="O208" s="8"/>
       <c r="P208" s="1" t="str">
         <f t="shared" si="3"/>
         <v>12/08/2026</v>
       </c>
-      <c r="Q208" s="17">
+      <c r="Q208" s="18">
         <v>46246</v>
       </c>
-      <c r="R208" s="18">
+      <c r="R208" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-3</v>
       </c>
     </row>
-    <row r="209" spans="1:18">
-      <c r="A209" s="6" t="s">
+    <row r="209" spans="1:18" hidden="1">
+      <c r="A209" s="7" t="s">
         <v>258</v>
       </c>
       <c r="B209" s="1" t="s">
@@ -15143,26 +15166,26 @@
         <v>87318</v>
       </c>
       <c r="M209" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="N209" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="N209" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O209" s="7"/>
+      <c r="O209" s="8"/>
       <c r="P209" s="1" t="str">
         <f t="shared" si="3"/>
         <v>8/3/2026</v>
       </c>
-      <c r="Q209" s="17">
+      <c r="Q209" s="18">
         <v>46089</v>
       </c>
-      <c r="R209" s="18">
+      <c r="R209" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-160</v>
       </c>
     </row>
-    <row r="210" spans="1:18">
-      <c r="A210" s="6" t="s">
+    <row r="210" spans="1:18" hidden="1">
+      <c r="A210" s="7" t="s">
         <v>194</v>
       </c>
       <c r="B210" s="1" t="s">
@@ -15199,26 +15222,26 @@
         <v>70694</v>
       </c>
       <c r="M210" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="N210" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="N210" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O210" s="7"/>
+      <c r="O210" s="8"/>
       <c r="P210" s="1" t="str">
         <f t="shared" si="3"/>
         <v>7/8/2026</v>
       </c>
-      <c r="Q210" s="17">
+      <c r="Q210" s="18">
         <v>46241</v>
       </c>
-      <c r="R210" s="18">
+      <c r="R210" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-8</v>
       </c>
     </row>
-    <row r="211" spans="1:18">
-      <c r="A211" s="6" t="s">
+    <row r="211" spans="1:18" hidden="1">
+      <c r="A211" s="7" t="s">
         <v>274</v>
       </c>
       <c r="B211" s="1" t="s">
@@ -15255,26 +15278,26 @@
         <v>63119</v>
       </c>
       <c r="M211" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="N211" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="N211" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O211" s="7"/>
+      <c r="O211" s="8"/>
       <c r="P211" s="1" t="str">
         <f t="shared" si="3"/>
         <v>10/8/2026</v>
       </c>
-      <c r="Q211" s="17">
+      <c r="Q211" s="18">
         <v>46244</v>
       </c>
-      <c r="R211" s="18">
+      <c r="R211" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-5</v>
       </c>
     </row>
-    <row r="212" spans="1:18">
-      <c r="A212" s="6" t="s">
+    <row r="212" spans="1:18" hidden="1">
+      <c r="A212" s="7" t="s">
         <v>192</v>
       </c>
       <c r="B212" s="1" t="s">
@@ -15311,26 +15334,26 @@
         <v>61702</v>
       </c>
       <c r="M212" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="N212" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="N212" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O212" s="7"/>
+      <c r="O212" s="8"/>
       <c r="P212" s="1" t="str">
         <f t="shared" si="3"/>
         <v>6/8/2026</v>
       </c>
-      <c r="Q212" s="17">
+      <c r="Q212" s="18">
         <v>46240</v>
       </c>
-      <c r="R212" s="18">
+      <c r="R212" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-9</v>
       </c>
     </row>
-    <row r="213" spans="1:18">
-      <c r="A213" s="6" t="s">
+    <row r="213" spans="1:18" hidden="1">
+      <c r="A213" s="7" t="s">
         <v>189</v>
       </c>
       <c r="B213" s="1" t="s">
@@ -15367,26 +15390,26 @@
         <v>55875</v>
       </c>
       <c r="M213" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="N213" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="N213" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O213" s="7"/>
+      <c r="O213" s="8"/>
       <c r="P213" s="1" t="str">
         <f t="shared" si="3"/>
         <v>12/8/2026</v>
       </c>
-      <c r="Q213" s="17">
+      <c r="Q213" s="18">
         <v>46246</v>
       </c>
-      <c r="R213" s="18">
+      <c r="R213" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-3</v>
       </c>
     </row>
-    <row r="214" spans="1:18">
-      <c r="A214" s="6" t="s">
+    <row r="214" spans="1:18" hidden="1">
+      <c r="A214" s="7" t="s">
         <v>423</v>
       </c>
       <c r="B214" s="1" t="s">
@@ -15423,26 +15446,26 @@
         <v>53002</v>
       </c>
       <c r="M214" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="N214" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="N214" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O214" s="7"/>
+      <c r="O214" s="8"/>
       <c r="P214" s="1" t="str">
         <f t="shared" si="3"/>
         <v>23/06/2026</v>
       </c>
-      <c r="Q214" s="17">
+      <c r="Q214" s="18">
         <v>46196</v>
       </c>
-      <c r="R214" s="18">
+      <c r="R214" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-53</v>
       </c>
     </row>
     <row r="215" spans="1:18">
-      <c r="A215" s="6" t="s">
+      <c r="A215" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B215" s="1" t="s">
@@ -15457,7 +15480,7 @@
       <c r="E215" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F215" s="1">
+      <c r="F215" s="2">
         <v>149450.00000999999</v>
       </c>
       <c r="G215" s="1" t="s">
@@ -15479,28 +15502,28 @@
         <v>30173201</v>
       </c>
       <c r="M215" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="N215" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O215" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="N215" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O215" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="P215" s="1" t="e">
+      <c r="P215" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q215" s="17" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="R215" s="18" t="e">
-        <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="216" spans="1:18">
-      <c r="A216" s="6" t="s">
+        <v xml:space="preserve">	01/06/2026</v>
+      </c>
+      <c r="Q215" s="18">
+        <v>46174</v>
+      </c>
+      <c r="R215" s="19">
+        <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
+        <v>-75</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" hidden="1">
+      <c r="A216" s="7" t="s">
         <v>205</v>
       </c>
       <c r="B216" s="1" t="s">
@@ -15537,26 +15560,26 @@
         <v>19308</v>
       </c>
       <c r="M216" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="N216" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="N216" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="O216" s="7"/>
+      <c r="O216" s="8"/>
       <c r="P216" s="1" t="str">
         <f t="shared" si="3"/>
         <v>7/8/2026</v>
       </c>
-      <c r="Q216" s="17">
+      <c r="Q216" s="18">
         <v>46241</v>
       </c>
-      <c r="R216" s="18">
+      <c r="R216" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-8</v>
       </c>
     </row>
     <row r="217" spans="1:18">
-      <c r="A217" s="6" t="s">
+      <c r="A217" s="7" t="s">
         <v>178</v>
       </c>
       <c r="B217" s="1" t="s">
@@ -15571,7 +15594,7 @@
       <c r="E217" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F217" s="1">
+      <c r="F217" s="2">
         <v>237.49628000000001</v>
       </c>
       <c r="G217" s="1" t="s">
@@ -15593,78 +15616,78 @@
         <v>56497243</v>
       </c>
       <c r="M217" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="N217" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="O217" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="N217" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="O217" s="8" t="s">
         <v>460</v>
       </c>
       <c r="P217" s="1" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="Q217" s="17" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="R217" s="18" t="e">
-        <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="218" spans="1:18">
-      <c r="A218" s="8" t="s">
+      <c r="Q217" s="18">
+        <v>46221</v>
+      </c>
+      <c r="R217" s="19">
+        <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" hidden="1">
+      <c r="A218" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B218" s="9" t="s">
+      <c r="B218" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="C218" s="9">
+      <c r="C218" s="10">
         <v>1</v>
       </c>
-      <c r="D218" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E218" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F218" s="9">
+      <c r="D218" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E218" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F218" s="10">
         <v>1</v>
       </c>
-      <c r="G218" s="9" t="s">
+      <c r="G218" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="H218" s="9" t="s">
+      <c r="H218" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="I218" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J218" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K218" s="9">
+      <c r="I218" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J218" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K218" s="10">
         <v>8051</v>
       </c>
-      <c r="L218" s="10">
+      <c r="L218" s="11">
         <v>8051</v>
       </c>
-      <c r="M218" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="N218" s="11" t="s">
+      <c r="M218" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="N218" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="O218" s="11"/>
-      <c r="P218" s="9" t="str">
+      <c r="O218" s="12"/>
+      <c r="P218" s="10" t="str">
         <f t="shared" si="3"/>
         <v>7/8/2026</v>
       </c>
-      <c r="Q218" s="17">
+      <c r="Q218" s="18">
         <v>46241</v>
       </c>
-      <c r="R218" s="18">
+      <c r="R218" s="19">
         <f ca="1">Table13[[#This Row],[Column1]]-TODAY()</f>
         <v>-8</v>
       </c>

--- a/Write off stock QC.xlsx
+++ b/Write off stock QC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8396F997-399C-4865-881A-271D6B506BF5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55710FC0-09CF-4B16-8180-EFD1CEA838B5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{09A0D57F-1F4F-4A67-AD02-CF0FEEFE867F}"/>
   </bookViews>
@@ -2768,14 +2768,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AA967156-E67F-411F-9430-CE31B28DDA10}" name="Table13" displayName="Table13" ref="A1:R218" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21" headerRowBorderDxfId="19" tableBorderDxfId="20" totalsRowBorderDxfId="18" headerRowCellStyle="Comma">
-  <autoFilter ref="A1:R218" xr:uid="{D100E3CB-680C-4696-9614-C02863D70058}">
-    <filterColumn colId="16">
-      <filters>
-        <filter val="#VALUE!"/>
-        <filter val="#N/A"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <sortState ref="A2:R215">
     <sortCondition descending="1" ref="L1:L218"/>
   </sortState>
@@ -3195,7 +3187,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="2" spans="1:18" hidden="1">
+    <row r="2" spans="1:18">
       <c r="A2" s="7" t="s">
         <v>241</v>
       </c>
@@ -3253,7 +3245,7 @@
         <v>-880</v>
       </c>
     </row>
-    <row r="3" spans="1:18" hidden="1">
+    <row r="3" spans="1:18">
       <c r="A3" s="7" t="s">
         <v>244</v>
       </c>
@@ -3311,7 +3303,7 @@
         <v>-880</v>
       </c>
     </row>
-    <row r="4" spans="1:18" hidden="1">
+    <row r="4" spans="1:18">
       <c r="A4" s="7" t="s">
         <v>247</v>
       </c>
@@ -3369,7 +3361,7 @@
         <v>-880</v>
       </c>
     </row>
-    <row r="5" spans="1:18" hidden="1">
+    <row r="5" spans="1:18">
       <c r="A5" s="7" t="s">
         <v>434</v>
       </c>
@@ -3427,7 +3419,7 @@
         <v>-326</v>
       </c>
     </row>
-    <row r="6" spans="1:18" hidden="1">
+    <row r="6" spans="1:18">
       <c r="A6" s="7" t="s">
         <v>437</v>
       </c>
@@ -3485,7 +3477,7 @@
         <v>-326</v>
       </c>
     </row>
-    <row r="7" spans="1:18" hidden="1">
+    <row r="7" spans="1:18">
       <c r="A7" s="7" t="s">
         <v>222</v>
       </c>
@@ -3543,7 +3535,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="8" spans="1:18" hidden="1">
+    <row r="8" spans="1:18">
       <c r="A8" s="6" t="s">
         <v>210</v>
       </c>
@@ -3601,7 +3593,7 @@
         <v>-466</v>
       </c>
     </row>
-    <row r="9" spans="1:18" hidden="1">
+    <row r="9" spans="1:18">
       <c r="A9" s="7" t="s">
         <v>213</v>
       </c>
@@ -3657,7 +3649,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="10" spans="1:18" hidden="1">
+    <row r="10" spans="1:18">
       <c r="A10" s="7" t="s">
         <v>76</v>
       </c>
@@ -3715,7 +3707,7 @@
         <v>-403</v>
       </c>
     </row>
-    <row r="11" spans="1:18" hidden="1">
+    <row r="11" spans="1:18">
       <c r="A11" s="7" t="s">
         <v>408</v>
       </c>
@@ -3771,7 +3763,7 @@
         <v>-49</v>
       </c>
     </row>
-    <row r="12" spans="1:18" hidden="1">
+    <row r="12" spans="1:18">
       <c r="A12" s="7" t="s">
         <v>265</v>
       </c>
@@ -3829,7 +3821,7 @@
         <v>-238</v>
       </c>
     </row>
-    <row r="13" spans="1:18" hidden="1">
+    <row r="13" spans="1:18">
       <c r="A13" s="7" t="s">
         <v>401</v>
       </c>
@@ -3885,7 +3877,7 @@
         <v>-151</v>
       </c>
     </row>
-    <row r="14" spans="1:18" hidden="1">
+    <row r="14" spans="1:18">
       <c r="A14" s="7" t="s">
         <v>267</v>
       </c>
@@ -3941,7 +3933,7 @@
         <v>-308</v>
       </c>
     </row>
-    <row r="15" spans="1:18" hidden="1">
+    <row r="15" spans="1:18">
       <c r="A15" s="6" t="s">
         <v>167</v>
       </c>
@@ -3997,7 +3989,7 @@
         <v>-353</v>
       </c>
     </row>
-    <row r="16" spans="1:18" hidden="1">
+    <row r="16" spans="1:18">
       <c r="A16" s="7" t="s">
         <v>31</v>
       </c>
@@ -4055,7 +4047,7 @@
         <v>-162</v>
       </c>
     </row>
-    <row r="17" spans="1:18" hidden="1">
+    <row r="17" spans="1:18">
       <c r="A17" s="7" t="s">
         <v>35</v>
       </c>
@@ -4113,7 +4105,7 @@
         <v>-162</v>
       </c>
     </row>
-    <row r="18" spans="1:18" hidden="1">
+    <row r="18" spans="1:18">
       <c r="A18" s="7" t="s">
         <v>207</v>
       </c>
@@ -4169,7 +4161,7 @@
         <v>-766</v>
       </c>
     </row>
-    <row r="19" spans="1:18" hidden="1">
+    <row r="19" spans="1:18">
       <c r="A19" s="7" t="s">
         <v>128</v>
       </c>
@@ -4225,7 +4217,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="20" spans="1:18" hidden="1">
+    <row r="20" spans="1:18">
       <c r="A20" s="7" t="s">
         <v>27</v>
       </c>
@@ -4283,7 +4275,7 @@
         <v>-138</v>
       </c>
     </row>
-    <row r="21" spans="1:18" hidden="1">
+    <row r="21" spans="1:18">
       <c r="A21" s="7" t="s">
         <v>33</v>
       </c>
@@ -4341,7 +4333,7 @@
         <v>-138</v>
       </c>
     </row>
-    <row r="22" spans="1:18" hidden="1">
+    <row r="22" spans="1:18">
       <c r="A22" s="7" t="s">
         <v>37</v>
       </c>
@@ -4399,7 +4391,7 @@
         <v>-138</v>
       </c>
     </row>
-    <row r="23" spans="1:18" hidden="1">
+    <row r="23" spans="1:18">
       <c r="A23" s="7" t="s">
         <v>255</v>
       </c>
@@ -4457,7 +4449,7 @@
         <v>-96</v>
       </c>
     </row>
-    <row r="24" spans="1:18" hidden="1">
+    <row r="24" spans="1:18">
       <c r="A24" s="7" t="s">
         <v>80</v>
       </c>
@@ -4515,7 +4507,7 @@
         <v>-409</v>
       </c>
     </row>
-    <row r="25" spans="1:18" hidden="1">
+    <row r="25" spans="1:18">
       <c r="A25" s="6" t="s">
         <v>12</v>
       </c>
@@ -4573,7 +4565,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="26" spans="1:18" hidden="1">
+    <row r="26" spans="1:18">
       <c r="A26" s="7" t="s">
         <v>18</v>
       </c>
@@ -4631,7 +4623,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="27" spans="1:18" hidden="1">
+    <row r="27" spans="1:18">
       <c r="A27" s="7" t="s">
         <v>21</v>
       </c>
@@ -4689,7 +4681,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="28" spans="1:18" hidden="1">
+    <row r="28" spans="1:18">
       <c r="A28" s="7" t="s">
         <v>41</v>
       </c>
@@ -4747,7 +4739,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="29" spans="1:18" hidden="1">
+    <row r="29" spans="1:18">
       <c r="A29" s="7" t="s">
         <v>43</v>
       </c>
@@ -4805,7 +4797,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="30" spans="1:18" hidden="1">
+    <row r="30" spans="1:18">
       <c r="A30" s="7" t="s">
         <v>45</v>
       </c>
@@ -4863,7 +4855,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="31" spans="1:18" hidden="1">
+    <row r="31" spans="1:18">
       <c r="A31" s="7" t="s">
         <v>47</v>
       </c>
@@ -4921,7 +4913,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="32" spans="1:18" hidden="1">
+    <row r="32" spans="1:18">
       <c r="A32" s="7" t="s">
         <v>49</v>
       </c>
@@ -4979,7 +4971,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="33" spans="1:18" hidden="1">
+    <row r="33" spans="1:18">
       <c r="A33" s="7" t="s">
         <v>50</v>
       </c>
@@ -5037,7 +5029,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="34" spans="1:18" hidden="1">
+    <row r="34" spans="1:18">
       <c r="A34" s="7" t="s">
         <v>52</v>
       </c>
@@ -5095,7 +5087,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="35" spans="1:18" hidden="1">
+    <row r="35" spans="1:18">
       <c r="A35" s="7" t="s">
         <v>58</v>
       </c>
@@ -5153,7 +5145,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="36" spans="1:18" hidden="1">
+    <row r="36" spans="1:18">
       <c r="A36" s="7" t="s">
         <v>60</v>
       </c>
@@ -5211,7 +5203,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="37" spans="1:18" hidden="1">
+    <row r="37" spans="1:18">
       <c r="A37" s="7" t="s">
         <v>63</v>
       </c>
@@ -5269,7 +5261,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="38" spans="1:18" hidden="1">
+    <row r="38" spans="1:18">
       <c r="A38" s="7" t="s">
         <v>65</v>
       </c>
@@ -5327,7 +5319,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="39" spans="1:18" hidden="1">
+    <row r="39" spans="1:18">
       <c r="A39" s="7" t="s">
         <v>68</v>
       </c>
@@ -5385,7 +5377,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="40" spans="1:18" hidden="1">
+    <row r="40" spans="1:18">
       <c r="A40" s="7" t="s">
         <v>71</v>
       </c>
@@ -5443,7 +5435,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="41" spans="1:18" hidden="1">
+    <row r="41" spans="1:18">
       <c r="A41" s="7" t="s">
         <v>73</v>
       </c>
@@ -5501,7 +5493,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="42" spans="1:18" hidden="1">
+    <row r="42" spans="1:18">
       <c r="A42" s="7" t="s">
         <v>86</v>
       </c>
@@ -5559,7 +5551,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="43" spans="1:18" hidden="1">
+    <row r="43" spans="1:18">
       <c r="A43" s="7" t="s">
         <v>97</v>
       </c>
@@ -5617,7 +5609,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="44" spans="1:18" hidden="1">
+    <row r="44" spans="1:18">
       <c r="A44" s="7" t="s">
         <v>99</v>
       </c>
@@ -5675,7 +5667,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="45" spans="1:18" hidden="1">
+    <row r="45" spans="1:18">
       <c r="A45" s="7" t="s">
         <v>102</v>
       </c>
@@ -5733,7 +5725,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="46" spans="1:18" hidden="1">
+    <row r="46" spans="1:18">
       <c r="A46" s="7" t="s">
         <v>104</v>
       </c>
@@ -5791,7 +5783,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="47" spans="1:18" hidden="1">
+    <row r="47" spans="1:18">
       <c r="A47" s="7" t="s">
         <v>105</v>
       </c>
@@ -5849,7 +5841,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="48" spans="1:18" hidden="1">
+    <row r="48" spans="1:18">
       <c r="A48" s="7" t="s">
         <v>106</v>
       </c>
@@ -5907,7 +5899,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="49" spans="1:18" hidden="1">
+    <row r="49" spans="1:18">
       <c r="A49" s="7" t="s">
         <v>107</v>
       </c>
@@ -5965,7 +5957,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="50" spans="1:18" hidden="1">
+    <row r="50" spans="1:18">
       <c r="A50" s="7" t="s">
         <v>109</v>
       </c>
@@ -6023,7 +6015,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="51" spans="1:18" hidden="1">
+    <row r="51" spans="1:18">
       <c r="A51" s="7" t="s">
         <v>114</v>
       </c>
@@ -6081,7 +6073,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="52" spans="1:18" hidden="1">
+    <row r="52" spans="1:18">
       <c r="A52" s="7" t="s">
         <v>117</v>
       </c>
@@ -6139,7 +6131,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="53" spans="1:18" hidden="1">
+    <row r="53" spans="1:18">
       <c r="A53" s="7" t="s">
         <v>119</v>
       </c>
@@ -6197,7 +6189,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="54" spans="1:18" hidden="1">
+    <row r="54" spans="1:18">
       <c r="A54" s="7" t="s">
         <v>121</v>
       </c>
@@ -6255,7 +6247,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="55" spans="1:18" hidden="1">
+    <row r="55" spans="1:18">
       <c r="A55" s="7" t="s">
         <v>123</v>
       </c>
@@ -6313,7 +6305,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="56" spans="1:18" hidden="1">
+    <row r="56" spans="1:18">
       <c r="A56" s="7" t="s">
         <v>130</v>
       </c>
@@ -6371,7 +6363,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="57" spans="1:18" hidden="1">
+    <row r="57" spans="1:18">
       <c r="A57" s="7" t="s">
         <v>134</v>
       </c>
@@ -6429,7 +6421,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="58" spans="1:18" hidden="1">
+    <row r="58" spans="1:18">
       <c r="A58" s="7" t="s">
         <v>136</v>
       </c>
@@ -6487,7 +6479,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="59" spans="1:18" hidden="1">
+    <row r="59" spans="1:18">
       <c r="A59" s="7" t="s">
         <v>138</v>
       </c>
@@ -6545,7 +6537,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="60" spans="1:18" hidden="1">
+    <row r="60" spans="1:18">
       <c r="A60" s="7" t="s">
         <v>140</v>
       </c>
@@ -6603,7 +6595,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="61" spans="1:18" hidden="1">
+    <row r="61" spans="1:18">
       <c r="A61" s="7" t="s">
         <v>141</v>
       </c>
@@ -6661,7 +6653,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="62" spans="1:18" hidden="1">
+    <row r="62" spans="1:18">
       <c r="A62" s="7" t="s">
         <v>143</v>
       </c>
@@ -6719,7 +6711,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="63" spans="1:18" hidden="1">
+    <row r="63" spans="1:18">
       <c r="A63" s="7" t="s">
         <v>145</v>
       </c>
@@ -6777,7 +6769,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="64" spans="1:18" hidden="1">
+    <row r="64" spans="1:18">
       <c r="A64" s="7" t="s">
         <v>147</v>
       </c>
@@ -6835,7 +6827,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="65" spans="1:18" hidden="1">
+    <row r="65" spans="1:18">
       <c r="A65" s="7" t="s">
         <v>149</v>
       </c>
@@ -6893,7 +6885,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="66" spans="1:18" hidden="1">
+    <row r="66" spans="1:18">
       <c r="A66" s="7" t="s">
         <v>151</v>
       </c>
@@ -6951,7 +6943,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="67" spans="1:18" hidden="1">
+    <row r="67" spans="1:18">
       <c r="A67" s="7" t="s">
         <v>153</v>
       </c>
@@ -7009,7 +7001,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="68" spans="1:18" hidden="1">
+    <row r="68" spans="1:18">
       <c r="A68" s="7" t="s">
         <v>155</v>
       </c>
@@ -7067,7 +7059,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="69" spans="1:18" hidden="1">
+    <row r="69" spans="1:18">
       <c r="A69" s="7" t="s">
         <v>157</v>
       </c>
@@ -7125,7 +7117,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="70" spans="1:18" hidden="1">
+    <row r="70" spans="1:18">
       <c r="A70" s="7" t="s">
         <v>159</v>
       </c>
@@ -7183,7 +7175,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="71" spans="1:18" hidden="1">
+    <row r="71" spans="1:18">
       <c r="A71" s="7" t="s">
         <v>161</v>
       </c>
@@ -7241,7 +7233,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="72" spans="1:18" hidden="1">
+    <row r="72" spans="1:18">
       <c r="A72" s="7" t="s">
         <v>163</v>
       </c>
@@ -7299,7 +7291,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="73" spans="1:18" hidden="1">
+    <row r="73" spans="1:18">
       <c r="A73" s="7" t="s">
         <v>174</v>
       </c>
@@ -7357,7 +7349,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="74" spans="1:18" hidden="1">
+    <row r="74" spans="1:18">
       <c r="A74" s="7" t="s">
         <v>176</v>
       </c>
@@ -7415,7 +7407,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="75" spans="1:18" hidden="1">
+    <row r="75" spans="1:18">
       <c r="A75" s="7" t="s">
         <v>181</v>
       </c>
@@ -7473,7 +7465,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="76" spans="1:18" hidden="1">
+    <row r="76" spans="1:18">
       <c r="A76" s="7" t="s">
         <v>185</v>
       </c>
@@ -7531,7 +7523,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="77" spans="1:18" hidden="1">
+    <row r="77" spans="1:18">
       <c r="A77" s="7" t="s">
         <v>187</v>
       </c>
@@ -7589,7 +7581,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="78" spans="1:18" hidden="1">
+    <row r="78" spans="1:18">
       <c r="A78" s="7" t="s">
         <v>201</v>
       </c>
@@ -7647,7 +7639,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="79" spans="1:18" hidden="1">
+    <row r="79" spans="1:18">
       <c r="A79" s="7" t="s">
         <v>215</v>
       </c>
@@ -7705,7 +7697,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="80" spans="1:18" hidden="1">
+    <row r="80" spans="1:18">
       <c r="A80" s="7" t="s">
         <v>217</v>
       </c>
@@ -7763,7 +7755,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="81" spans="1:18" hidden="1">
+    <row r="81" spans="1:18">
       <c r="A81" s="7" t="s">
         <v>220</v>
       </c>
@@ -7821,7 +7813,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="82" spans="1:18" hidden="1">
+    <row r="82" spans="1:18">
       <c r="A82" s="7" t="s">
         <v>225</v>
       </c>
@@ -7879,7 +7871,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="83" spans="1:18" hidden="1">
+    <row r="83" spans="1:18">
       <c r="A83" s="7" t="s">
         <v>226</v>
       </c>
@@ -7937,7 +7929,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="84" spans="1:18" hidden="1">
+    <row r="84" spans="1:18">
       <c r="A84" s="7" t="s">
         <v>228</v>
       </c>
@@ -7995,7 +7987,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="85" spans="1:18" hidden="1">
+    <row r="85" spans="1:18">
       <c r="A85" s="7" t="s">
         <v>230</v>
       </c>
@@ -8053,7 +8045,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="86" spans="1:18" hidden="1">
+    <row r="86" spans="1:18">
       <c r="A86" s="7" t="s">
         <v>233</v>
       </c>
@@ -8111,7 +8103,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="87" spans="1:18" hidden="1">
+    <row r="87" spans="1:18">
       <c r="A87" s="7" t="s">
         <v>277</v>
       </c>
@@ -8169,7 +8161,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="88" spans="1:18" hidden="1">
+    <row r="88" spans="1:18">
       <c r="A88" s="7" t="s">
         <v>283</v>
       </c>
@@ -8227,7 +8219,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="89" spans="1:18" hidden="1">
+    <row r="89" spans="1:18">
       <c r="A89" s="7" t="s">
         <v>285</v>
       </c>
@@ -8285,7 +8277,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="90" spans="1:18" hidden="1">
+    <row r="90" spans="1:18">
       <c r="A90" s="7" t="s">
         <v>288</v>
       </c>
@@ -8343,7 +8335,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="91" spans="1:18" hidden="1">
+    <row r="91" spans="1:18">
       <c r="A91" s="7" t="s">
         <v>290</v>
       </c>
@@ -8401,7 +8393,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="92" spans="1:18" hidden="1">
+    <row r="92" spans="1:18">
       <c r="A92" s="7" t="s">
         <v>291</v>
       </c>
@@ -8459,7 +8451,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="93" spans="1:18" hidden="1">
+    <row r="93" spans="1:18">
       <c r="A93" s="7" t="s">
         <v>293</v>
       </c>
@@ -8517,7 +8509,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="94" spans="1:18" hidden="1">
+    <row r="94" spans="1:18">
       <c r="A94" s="7" t="s">
         <v>295</v>
       </c>
@@ -8575,7 +8567,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="95" spans="1:18" hidden="1">
+    <row r="95" spans="1:18">
       <c r="A95" s="7" t="s">
         <v>299</v>
       </c>
@@ -8633,7 +8625,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="96" spans="1:18" hidden="1">
+    <row r="96" spans="1:18">
       <c r="A96" s="7" t="s">
         <v>301</v>
       </c>
@@ -8691,7 +8683,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="97" spans="1:18" hidden="1">
+    <row r="97" spans="1:18">
       <c r="A97" s="7" t="s">
         <v>303</v>
       </c>
@@ -8749,7 +8741,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="98" spans="1:18" hidden="1">
+    <row r="98" spans="1:18">
       <c r="A98" s="7" t="s">
         <v>304</v>
       </c>
@@ -8807,7 +8799,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="99" spans="1:18" hidden="1">
+    <row r="99" spans="1:18">
       <c r="A99" s="7" t="s">
         <v>306</v>
       </c>
@@ -8865,7 +8857,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="100" spans="1:18" hidden="1">
+    <row r="100" spans="1:18">
       <c r="A100" s="7" t="s">
         <v>307</v>
       </c>
@@ -8923,7 +8915,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="101" spans="1:18" hidden="1">
+    <row r="101" spans="1:18">
       <c r="A101" s="7" t="s">
         <v>308</v>
       </c>
@@ -8981,7 +8973,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="102" spans="1:18" hidden="1">
+    <row r="102" spans="1:18">
       <c r="A102" s="7" t="s">
         <v>310</v>
       </c>
@@ -9039,7 +9031,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="103" spans="1:18" hidden="1">
+    <row r="103" spans="1:18">
       <c r="A103" s="7" t="s">
         <v>313</v>
       </c>
@@ -9097,7 +9089,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="104" spans="1:18" hidden="1">
+    <row r="104" spans="1:18">
       <c r="A104" s="7" t="s">
         <v>315</v>
       </c>
@@ -9155,7 +9147,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="105" spans="1:18" hidden="1">
+    <row r="105" spans="1:18">
       <c r="A105" s="7" t="s">
         <v>316</v>
       </c>
@@ -9213,7 +9205,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="106" spans="1:18" hidden="1">
+    <row r="106" spans="1:18">
       <c r="A106" s="7" t="s">
         <v>318</v>
       </c>
@@ -9271,7 +9263,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="107" spans="1:18" hidden="1">
+    <row r="107" spans="1:18">
       <c r="A107" s="7" t="s">
         <v>319</v>
       </c>
@@ -9329,7 +9321,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="108" spans="1:18" hidden="1">
+    <row r="108" spans="1:18">
       <c r="A108" s="7" t="s">
         <v>320</v>
       </c>
@@ -9387,7 +9379,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="109" spans="1:18" hidden="1">
+    <row r="109" spans="1:18">
       <c r="A109" s="7" t="s">
         <v>322</v>
       </c>
@@ -9445,7 +9437,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="110" spans="1:18" hidden="1">
+    <row r="110" spans="1:18">
       <c r="A110" s="7" t="s">
         <v>324</v>
       </c>
@@ -9503,7 +9495,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="111" spans="1:18" hidden="1">
+    <row r="111" spans="1:18">
       <c r="A111" s="7" t="s">
         <v>325</v>
       </c>
@@ -9561,7 +9553,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="112" spans="1:18" hidden="1">
+    <row r="112" spans="1:18">
       <c r="A112" s="7" t="s">
         <v>326</v>
       </c>
@@ -9619,7 +9611,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="113" spans="1:18" hidden="1">
+    <row r="113" spans="1:18">
       <c r="A113" s="7" t="s">
         <v>327</v>
       </c>
@@ -9677,7 +9669,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="114" spans="1:18" hidden="1">
+    <row r="114" spans="1:18">
       <c r="A114" s="7" t="s">
         <v>328</v>
       </c>
@@ -9735,7 +9727,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="115" spans="1:18" hidden="1">
+    <row r="115" spans="1:18">
       <c r="A115" s="7" t="s">
         <v>329</v>
       </c>
@@ -9793,7 +9785,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="116" spans="1:18" hidden="1">
+    <row r="116" spans="1:18">
       <c r="A116" s="7" t="s">
         <v>330</v>
       </c>
@@ -9851,7 +9843,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="117" spans="1:18" hidden="1">
+    <row r="117" spans="1:18">
       <c r="A117" s="7" t="s">
         <v>332</v>
       </c>
@@ -9909,7 +9901,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="118" spans="1:18" hidden="1">
+    <row r="118" spans="1:18">
       <c r="A118" s="7" t="s">
         <v>333</v>
       </c>
@@ -9967,7 +9959,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="119" spans="1:18" hidden="1">
+    <row r="119" spans="1:18">
       <c r="A119" s="7" t="s">
         <v>334</v>
       </c>
@@ -10025,7 +10017,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="120" spans="1:18" hidden="1">
+    <row r="120" spans="1:18">
       <c r="A120" s="7" t="s">
         <v>335</v>
       </c>
@@ -10083,7 +10075,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="121" spans="1:18" hidden="1">
+    <row r="121" spans="1:18">
       <c r="A121" s="7" t="s">
         <v>336</v>
       </c>
@@ -10141,7 +10133,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="122" spans="1:18" hidden="1">
+    <row r="122" spans="1:18">
       <c r="A122" s="7" t="s">
         <v>337</v>
       </c>
@@ -10199,7 +10191,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="123" spans="1:18" hidden="1">
+    <row r="123" spans="1:18">
       <c r="A123" s="7" t="s">
         <v>339</v>
       </c>
@@ -10257,7 +10249,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="124" spans="1:18" hidden="1">
+    <row r="124" spans="1:18">
       <c r="A124" s="7" t="s">
         <v>341</v>
       </c>
@@ -10315,7 +10307,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="125" spans="1:18" hidden="1">
+    <row r="125" spans="1:18">
       <c r="A125" s="7" t="s">
         <v>342</v>
       </c>
@@ -10373,7 +10365,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="126" spans="1:18" hidden="1">
+    <row r="126" spans="1:18">
       <c r="A126" s="7" t="s">
         <v>343</v>
       </c>
@@ -10431,7 +10423,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="127" spans="1:18" hidden="1">
+    <row r="127" spans="1:18">
       <c r="A127" s="7" t="s">
         <v>344</v>
       </c>
@@ -10489,7 +10481,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="128" spans="1:18" hidden="1">
+    <row r="128" spans="1:18">
       <c r="A128" s="7" t="s">
         <v>345</v>
       </c>
@@ -10547,7 +10539,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="129" spans="1:18" hidden="1">
+    <row r="129" spans="1:18">
       <c r="A129" s="7" t="s">
         <v>347</v>
       </c>
@@ -10605,7 +10597,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="130" spans="1:18" hidden="1">
+    <row r="130" spans="1:18">
       <c r="A130" s="7" t="s">
         <v>348</v>
       </c>
@@ -10663,7 +10655,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="131" spans="1:18" hidden="1">
+    <row r="131" spans="1:18">
       <c r="A131" s="7" t="s">
         <v>349</v>
       </c>
@@ -10721,7 +10713,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="132" spans="1:18" hidden="1">
+    <row r="132" spans="1:18">
       <c r="A132" s="7" t="s">
         <v>351</v>
       </c>
@@ -10779,7 +10771,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="133" spans="1:18" hidden="1">
+    <row r="133" spans="1:18">
       <c r="A133" s="7" t="s">
         <v>353</v>
       </c>
@@ -10837,7 +10829,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="134" spans="1:18" hidden="1">
+    <row r="134" spans="1:18">
       <c r="A134" s="7" t="s">
         <v>356</v>
       </c>
@@ -10895,7 +10887,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="135" spans="1:18" hidden="1">
+    <row r="135" spans="1:18">
       <c r="A135" s="7" t="s">
         <v>358</v>
       </c>
@@ -10953,7 +10945,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="136" spans="1:18" hidden="1">
+    <row r="136" spans="1:18">
       <c r="A136" s="7" t="s">
         <v>359</v>
       </c>
@@ -11011,7 +11003,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="137" spans="1:18" hidden="1">
+    <row r="137" spans="1:18">
       <c r="A137" s="7" t="s">
         <v>362</v>
       </c>
@@ -11069,7 +11061,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="138" spans="1:18" hidden="1">
+    <row r="138" spans="1:18">
       <c r="A138" s="7" t="s">
         <v>364</v>
       </c>
@@ -11127,7 +11119,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="139" spans="1:18" hidden="1">
+    <row r="139" spans="1:18">
       <c r="A139" s="7" t="s">
         <v>365</v>
       </c>
@@ -11185,7 +11177,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="140" spans="1:18" hidden="1">
+    <row r="140" spans="1:18">
       <c r="A140" s="7" t="s">
         <v>367</v>
       </c>
@@ -11243,7 +11235,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="141" spans="1:18" hidden="1">
+    <row r="141" spans="1:18">
       <c r="A141" s="7" t="s">
         <v>368</v>
       </c>
@@ -11301,7 +11293,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="142" spans="1:18" hidden="1">
+    <row r="142" spans="1:18">
       <c r="A142" s="7" t="s">
         <v>369</v>
       </c>
@@ -11359,7 +11351,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="143" spans="1:18" hidden="1">
+    <row r="143" spans="1:18">
       <c r="A143" s="7" t="s">
         <v>371</v>
       </c>
@@ -11417,7 +11409,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="144" spans="1:18" hidden="1">
+    <row r="144" spans="1:18">
       <c r="A144" s="7" t="s">
         <v>372</v>
       </c>
@@ -11475,7 +11467,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="145" spans="1:18" hidden="1">
+    <row r="145" spans="1:18">
       <c r="A145" s="7" t="s">
         <v>373</v>
       </c>
@@ -11533,7 +11525,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="146" spans="1:18" hidden="1">
+    <row r="146" spans="1:18">
       <c r="A146" s="7" t="s">
         <v>374</v>
       </c>
@@ -11591,7 +11583,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="147" spans="1:18" hidden="1">
+    <row r="147" spans="1:18">
       <c r="A147" s="7" t="s">
         <v>377</v>
       </c>
@@ -11649,7 +11641,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="148" spans="1:18" hidden="1">
+    <row r="148" spans="1:18">
       <c r="A148" s="7" t="s">
         <v>378</v>
       </c>
@@ -11707,7 +11699,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="149" spans="1:18" hidden="1">
+    <row r="149" spans="1:18">
       <c r="A149" s="7" t="s">
         <v>380</v>
       </c>
@@ -11765,7 +11757,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="150" spans="1:18" hidden="1">
+    <row r="150" spans="1:18">
       <c r="A150" s="7" t="s">
         <v>381</v>
       </c>
@@ -11823,7 +11815,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="151" spans="1:18" hidden="1">
+    <row r="151" spans="1:18">
       <c r="A151" s="7" t="s">
         <v>382</v>
       </c>
@@ -11881,7 +11873,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="152" spans="1:18" hidden="1">
+    <row r="152" spans="1:18">
       <c r="A152" s="7" t="s">
         <v>383</v>
       </c>
@@ -11939,7 +11931,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="153" spans="1:18" hidden="1">
+    <row r="153" spans="1:18">
       <c r="A153" s="7" t="s">
         <v>384</v>
       </c>
@@ -11997,7 +11989,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="154" spans="1:18" hidden="1">
+    <row r="154" spans="1:18">
       <c r="A154" s="7" t="s">
         <v>385</v>
       </c>
@@ -12055,7 +12047,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="155" spans="1:18" hidden="1">
+    <row r="155" spans="1:18">
       <c r="A155" s="7" t="s">
         <v>387</v>
       </c>
@@ -12113,7 +12105,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="156" spans="1:18" hidden="1">
+    <row r="156" spans="1:18">
       <c r="A156" s="7" t="s">
         <v>388</v>
       </c>
@@ -12171,7 +12163,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="157" spans="1:18" hidden="1">
+    <row r="157" spans="1:18">
       <c r="A157" s="7" t="s">
         <v>389</v>
       </c>
@@ -12229,7 +12221,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="158" spans="1:18" hidden="1">
+    <row r="158" spans="1:18">
       <c r="A158" s="7" t="s">
         <v>390</v>
       </c>
@@ -12287,7 +12279,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="159" spans="1:18" hidden="1">
+    <row r="159" spans="1:18">
       <c r="A159" s="7" t="s">
         <v>395</v>
       </c>
@@ -12345,7 +12337,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="160" spans="1:18" hidden="1">
+    <row r="160" spans="1:18">
       <c r="A160" s="7" t="s">
         <v>397</v>
       </c>
@@ -12403,7 +12395,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="161" spans="1:18" hidden="1">
+    <row r="161" spans="1:18">
       <c r="A161" s="7" t="s">
         <v>398</v>
       </c>
@@ -12461,7 +12453,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="162" spans="1:18" hidden="1">
+    <row r="162" spans="1:18">
       <c r="A162" s="7" t="s">
         <v>399</v>
       </c>
@@ -12519,7 +12511,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="163" spans="1:18" hidden="1">
+    <row r="163" spans="1:18">
       <c r="A163" s="7" t="s">
         <v>403</v>
       </c>
@@ -12577,7 +12569,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="164" spans="1:18" hidden="1">
+    <row r="164" spans="1:18">
       <c r="A164" s="7" t="s">
         <v>405</v>
       </c>
@@ -12635,7 +12627,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="165" spans="1:18" hidden="1">
+    <row r="165" spans="1:18">
       <c r="A165" s="7" t="s">
         <v>407</v>
       </c>
@@ -12693,7 +12685,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="166" spans="1:18" hidden="1">
+    <row r="166" spans="1:18">
       <c r="A166" s="7" t="s">
         <v>410</v>
       </c>
@@ -12751,7 +12743,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="167" spans="1:18" hidden="1">
+    <row r="167" spans="1:18">
       <c r="A167" s="7" t="s">
         <v>412</v>
       </c>
@@ -12809,7 +12801,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="168" spans="1:18" hidden="1">
+    <row r="168" spans="1:18">
       <c r="A168" s="7" t="s">
         <v>413</v>
       </c>
@@ -12867,7 +12859,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="169" spans="1:18" hidden="1">
+    <row r="169" spans="1:18">
       <c r="A169" s="7" t="s">
         <v>415</v>
       </c>
@@ -12925,7 +12917,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="170" spans="1:18" hidden="1">
+    <row r="170" spans="1:18">
       <c r="A170" s="7" t="s">
         <v>417</v>
       </c>
@@ -12983,7 +12975,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="171" spans="1:18" hidden="1">
+    <row r="171" spans="1:18">
       <c r="A171" s="7" t="s">
         <v>418</v>
       </c>
@@ -13041,7 +13033,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="172" spans="1:18" hidden="1">
+    <row r="172" spans="1:18">
       <c r="A172" s="7" t="s">
         <v>420</v>
       </c>
@@ -13099,7 +13091,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="173" spans="1:18" hidden="1">
+    <row r="173" spans="1:18">
       <c r="A173" s="7" t="s">
         <v>424</v>
       </c>
@@ -13157,7 +13149,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="174" spans="1:18" hidden="1">
+    <row r="174" spans="1:18">
       <c r="A174" s="7" t="s">
         <v>426</v>
       </c>
@@ -13215,7 +13207,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="175" spans="1:18" hidden="1">
+    <row r="175" spans="1:18">
       <c r="A175" s="6" t="s">
         <v>428</v>
       </c>
@@ -13273,7 +13265,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="176" spans="1:18" hidden="1">
+    <row r="176" spans="1:18">
       <c r="A176" s="7" t="s">
         <v>430</v>
       </c>
@@ -13331,7 +13323,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="177" spans="1:18" hidden="1">
+    <row r="177" spans="1:18">
       <c r="A177" s="7" t="s">
         <v>440</v>
       </c>
@@ -13389,7 +13381,7 @@
         <v>-94</v>
       </c>
     </row>
-    <row r="178" spans="1:18" hidden="1">
+    <row r="178" spans="1:18">
       <c r="A178" s="7" t="s">
         <v>443</v>
       </c>
@@ -13502,7 +13494,7 @@
         <v>-86</v>
       </c>
     </row>
-    <row r="180" spans="1:18" hidden="1">
+    <row r="180" spans="1:18">
       <c r="A180" s="7" t="s">
         <v>409</v>
       </c>
@@ -13558,7 +13550,7 @@
         <v>-49</v>
       </c>
     </row>
-    <row r="181" spans="1:18" hidden="1">
+    <row r="181" spans="1:18">
       <c r="A181" s="7" t="s">
         <v>263</v>
       </c>
@@ -13616,7 +13608,7 @@
         <v>-72</v>
       </c>
     </row>
-    <row r="182" spans="1:18" hidden="1">
+    <row r="182" spans="1:18">
       <c r="A182" s="7" t="s">
         <v>93</v>
       </c>
@@ -13672,7 +13664,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="183" spans="1:18" hidden="1">
+    <row r="183" spans="1:18">
       <c r="A183" s="7" t="s">
         <v>203</v>
       </c>
@@ -13784,7 +13776,7 @@
         <v>-84</v>
       </c>
     </row>
-    <row r="185" spans="1:18" hidden="1">
+    <row r="185" spans="1:18">
       <c r="A185" s="7" t="s">
         <v>252</v>
       </c>
@@ -13840,7 +13832,7 @@
         <v>-23</v>
       </c>
     </row>
-    <row r="186" spans="1:18" hidden="1">
+    <row r="186" spans="1:18">
       <c r="A186" s="7" t="s">
         <v>53</v>
       </c>
@@ -13896,7 +13888,7 @@
         <v>-648</v>
       </c>
     </row>
-    <row r="187" spans="1:18" hidden="1">
+    <row r="187" spans="1:18">
       <c r="A187" s="7" t="s">
         <v>56</v>
       </c>
@@ -13952,7 +13944,7 @@
         <v>-648</v>
       </c>
     </row>
-    <row r="188" spans="1:18" hidden="1">
+    <row r="188" spans="1:18">
       <c r="A188" s="7" t="s">
         <v>125</v>
       </c>
@@ -14008,7 +14000,7 @@
         <v>-88</v>
       </c>
     </row>
-    <row r="189" spans="1:18" hidden="1">
+    <row r="189" spans="1:18">
       <c r="A189" s="7" t="s">
         <v>89</v>
       </c>
@@ -14064,7 +14056,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="190" spans="1:18" hidden="1">
+    <row r="190" spans="1:18">
       <c r="A190" s="7" t="s">
         <v>173</v>
       </c>
@@ -14120,7 +14112,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="191" spans="1:18" hidden="1">
+    <row r="191" spans="1:18">
       <c r="A191" s="7" t="s">
         <v>261</v>
       </c>
@@ -14176,7 +14168,7 @@
         <v>-95</v>
       </c>
     </row>
-    <row r="192" spans="1:18" hidden="1">
+    <row r="192" spans="1:18">
       <c r="A192" s="7" t="s">
         <v>235</v>
       </c>
@@ -14232,7 +14224,7 @@
         <v>-44</v>
       </c>
     </row>
-    <row r="193" spans="1:18" hidden="1">
+    <row r="193" spans="1:18">
       <c r="A193" s="7" t="s">
         <v>279</v>
       </c>
@@ -14288,7 +14280,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="194" spans="1:18" hidden="1">
+    <row r="194" spans="1:18">
       <c r="A194" s="7" t="s">
         <v>111</v>
       </c>
@@ -14344,7 +14336,7 @@
         <v>-26</v>
       </c>
     </row>
-    <row r="195" spans="1:18" hidden="1">
+    <row r="195" spans="1:18">
       <c r="A195" s="7" t="s">
         <v>164</v>
       </c>
@@ -14400,7 +14392,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="196" spans="1:18" hidden="1">
+    <row r="196" spans="1:18">
       <c r="A196" s="7" t="s">
         <v>24</v>
       </c>
@@ -14456,7 +14448,7 @@
         <v>-72</v>
       </c>
     </row>
-    <row r="197" spans="1:18" hidden="1">
+    <row r="197" spans="1:18">
       <c r="A197" s="7" t="s">
         <v>432</v>
       </c>
@@ -14512,7 +14504,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="198" spans="1:18" hidden="1">
+    <row r="198" spans="1:18">
       <c r="A198" s="7" t="s">
         <v>392</v>
       </c>
@@ -14568,7 +14560,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="199" spans="1:18" hidden="1">
+    <row r="199" spans="1:18">
       <c r="A199" s="7" t="s">
         <v>271</v>
       </c>
@@ -14624,7 +14616,7 @@
         <v>-26</v>
       </c>
     </row>
-    <row r="200" spans="1:18" hidden="1">
+    <row r="200" spans="1:18">
       <c r="A200" s="7" t="s">
         <v>95</v>
       </c>
@@ -14680,7 +14672,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="201" spans="1:18" hidden="1">
+    <row r="201" spans="1:18">
       <c r="A201" s="7" t="s">
         <v>239</v>
       </c>
@@ -14736,7 +14728,7 @@
         <v>-44</v>
       </c>
     </row>
-    <row r="202" spans="1:18" hidden="1">
+    <row r="202" spans="1:18">
       <c r="A202" s="7" t="s">
         <v>250</v>
       </c>
@@ -14792,7 +14784,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="203" spans="1:18" hidden="1">
+    <row r="203" spans="1:18">
       <c r="A203" s="7" t="s">
         <v>170</v>
       </c>
@@ -14848,7 +14840,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="204" spans="1:18" hidden="1">
+    <row r="204" spans="1:18">
       <c r="A204" s="7" t="s">
         <v>82</v>
       </c>
@@ -14904,7 +14896,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="205" spans="1:18" hidden="1">
+    <row r="205" spans="1:18">
       <c r="A205" s="7" t="s">
         <v>297</v>
       </c>
@@ -14960,7 +14952,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="206" spans="1:18" hidden="1">
+    <row r="206" spans="1:18">
       <c r="A206" s="7" t="s">
         <v>199</v>
       </c>
@@ -15016,7 +15008,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="207" spans="1:18" hidden="1">
+    <row r="207" spans="1:18">
       <c r="A207" s="7" t="s">
         <v>172</v>
       </c>
@@ -15072,7 +15064,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="208" spans="1:18" hidden="1">
+    <row r="208" spans="1:18">
       <c r="A208" s="7" t="s">
         <v>375</v>
       </c>
@@ -15128,7 +15120,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="209" spans="1:18" hidden="1">
+    <row r="209" spans="1:18">
       <c r="A209" s="7" t="s">
         <v>258</v>
       </c>
@@ -15184,7 +15176,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="210" spans="1:18" hidden="1">
+    <row r="210" spans="1:18">
       <c r="A210" s="7" t="s">
         <v>194</v>
       </c>
@@ -15240,7 +15232,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="211" spans="1:18" hidden="1">
+    <row r="211" spans="1:18">
       <c r="A211" s="7" t="s">
         <v>274</v>
       </c>
@@ -15296,7 +15288,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="212" spans="1:18" hidden="1">
+    <row r="212" spans="1:18">
       <c r="A212" s="7" t="s">
         <v>192</v>
       </c>
@@ -15352,7 +15344,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="213" spans="1:18" hidden="1">
+    <row r="213" spans="1:18">
       <c r="A213" s="7" t="s">
         <v>189</v>
       </c>
@@ -15408,7 +15400,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="214" spans="1:18" hidden="1">
+    <row r="214" spans="1:18">
       <c r="A214" s="7" t="s">
         <v>423</v>
       </c>
@@ -15522,7 +15514,7 @@
         <v>-75</v>
       </c>
     </row>
-    <row r="216" spans="1:18" hidden="1">
+    <row r="216" spans="1:18">
       <c r="A216" s="7" t="s">
         <v>205</v>
       </c>
@@ -15636,7 +15628,7 @@
         <v>-28</v>
       </c>
     </row>
-    <row r="218" spans="1:18" hidden="1">
+    <row r="218" spans="1:18">
       <c r="A218" s="9" t="s">
         <v>197</v>
       </c>

--- a/Write off stock QC.xlsx
+++ b/Write off stock QC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55710FC0-09CF-4B16-8180-EFD1CEA838B5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69571EF7-65A1-4544-B47F-6A8F87F7CDA1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{09A0D57F-1F4F-4A67-AD02-CF0FEEFE867F}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="523">
   <si>
     <t>Name</t>
   </si>
@@ -1583,6 +1583,12 @@
   </si>
   <si>
     <t xml:space="preserve">	01/06/2026_SANG QC_TBI Thiếu keo_CHờ hủy</t>
+  </si>
+  <si>
+    <t>18/07/2026</t>
+  </si>
+  <si>
+    <t>21/05/2026</t>
   </si>
 </sst>
 </file>
@@ -2695,13 +2701,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2718,6 +2717,13 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2767,7 +2773,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AA967156-E67F-411F-9430-CE31B28DDA10}" name="Table13" displayName="Table13" ref="A1:R218" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21" headerRowBorderDxfId="19" tableBorderDxfId="20" totalsRowBorderDxfId="18" headerRowCellStyle="Comma">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AA967156-E67F-411F-9430-CE31B28DDA10}" name="Table13" displayName="Table13" ref="A1:R218" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18" headerRowCellStyle="Comma">
+  <autoFilter ref="A1:R218" xr:uid="{27EFBAC1-E7FF-4C3F-BDA7-644013156F48}"/>
   <sortState ref="A2:R215">
     <sortCondition descending="1" ref="L1:L218"/>
   </sortState>
@@ -10644,7 +10651,7 @@
         <v>460</v>
       </c>
       <c r="P130" s="1" t="str">
-        <f t="shared" ref="P130:Q193" si="2">LEFT(M130,FIND("_",M130)-1)</f>
+        <f t="shared" ref="P130:P193" si="2">LEFT(M130,FIND("_",M130)-1)</f>
         <v>13/05/2026</v>
       </c>
       <c r="Q130" s="18">
@@ -13483,8 +13490,8 @@
         <v>459</v>
       </c>
       <c r="O179" s="8"/>
-      <c r="P179" s="22">
-        <v>46163</v>
+      <c r="P179" s="22" t="s">
+        <v>522</v>
       </c>
       <c r="Q179" s="18">
         <v>46163</v>
@@ -15616,9 +15623,8 @@
       <c r="O217" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="P217" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+      <c r="P217" s="18" t="s">
+        <v>521</v>
       </c>
       <c r="Q217" s="18">
         <v>46221</v>
